--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$46</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -915,8 +915,578 @@
         <v>45981.0</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>eth.illLink.text1</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>Article/chapter is not held in the swisscovery Network or cannot be requested.</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>Artikel/Kapitel ist im swisscovery Network nicht vorhanden oder nicht bestellbar.</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>45995.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>eth.illLink.text2</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>Please request via</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>Bestellen Sie bitte via</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>45995.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>eth.illLink.text3</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>45995.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>eth.illLink.linkText</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>interlibrary loan</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>Fernleihe</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>45995.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>eth.illLink.url</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>https://library.ethz.ch/en/searching-and-using/borrowing-and-using/order-forms/interlibrary-loans-ordering-copies.html</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>https://library.ethz.ch/recherchieren-und-nutzen/ausleihen-und-nutzen/bestellformulare/fernleihe-kopien-bestellen.html</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45995.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>eth.composeErara.print</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Print item in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>Print-Exemplar in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>eth.composeErara.online</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Online item in ETH swisscovery (from e-rara)</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Online-Exemplar in ETH swisscovery (e-rara)</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>eth.composeErara.emaps</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Georeferenced online item in ETH swisscovery (from e-maps)</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>Georeferenziertes Online-Exemplar in ETH swisscovery (e-maps)</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>eth.composeErara.geoTiff</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>GeoTIFF map via e-maps</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>GeoTIFF via e-maps</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>eth.composeNb.print</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>Print item in in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>Print-Exemplar in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>eth.composeNb.online</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Online item in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>Online-Exemplar in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>eth.dnbToc.toc</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Table of content from the DNB for </t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inhaltsverzeichnis der DNB zu </t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>eth.dnbToc.text</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Content description from the DNB for </t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inhaltstext der DNB zu </t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>eth.libraryStack.text1</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Password protected access. Restricted to members of ETH Zurich only.</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>Passwortgeschützter Zugang. Nur für Mitglieder der ETH Zürich zugänglich.</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>eth.libraryStack.text2</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>You need to register with your ETH Zurich e-mail address "Sign In". Access to this source is restricted on the domain ethz.ch because of license restrictions.</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>Sie müssen sich mit Ihrer ETH Zürich E-Mail-Adresse unter „Anmelden” registrieren. Der Zugriff auf diese Quelle ist aufgrund von Lizenzbeschränkungen auf die Domain ethz.ch eingeschränkt.</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>eth.wayback.text</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>In the web archive, select a year and a date marked in blue to access the archived website.</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Wählen Sie im Webarchiv ein Jahr und ein blau markiertes Datum, um die archivierte Website aufzurufen.</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>eth.wayback.linkText</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Link to the web archive</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>Link zum Webarchiv</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>45996.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>eth.onlineProblem.linkText</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Report access problem</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>Zugriffsproblem melden</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>45999.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>eth.onlineProblem.ariaLabel</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>Report access problem by email</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>Zugriffsproblem per E-Mail melden</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>45999.0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F27"/>
+  <autoFilter ref="A1:F46"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$85</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -96,7 +96,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.02734375" customWidth="true"/>
-    <col min="2" max="2" width="31.0234375" customWidth="true"/>
+    <col min="2" max="2" width="39.2421875" customWidth="true"/>
     <col min="3" max="3" width="255.0" customWidth="true"/>
     <col min="4" max="4" width="27.34375" customWidth="true"/>
     <col min="5" max="5" width="27.34375" customWidth="true"/>
@@ -1485,8 +1485,1178 @@
         <v>45999.0</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>eth.registrationLink.linkText</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>Not registered yet?</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>Noch nicht registriert?</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>45999.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>eth.onlineButton.linkText</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>View Online</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>Online anschauen</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>45999.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>eth.okm.label</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Search for “{{ search }}” in Open Knowledge Maps:</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>Suche nach “{{ search }}” in Open Knowledge Maps:</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>45999.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>eth.logoSubline.subline</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>eth.idpWarning.text1</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Link your SWICTH edu-ID to your ETH Zurich user account in </t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verknüpfen Sie Ihre SWITCH edu-ID mit Ihrem ETH-Benutzerkonto in </t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>eth.idpWarning.text2</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>to benefit from the advantages for members of ETH Zurich.</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>, um von den Vorteilen für ETH-Angehörige zu profitieren.</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>eth.idpWarning.linkText2</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Instructions</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>Anleitung</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>eth.idpWarning.linkText1</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>www.password.ethz.ch</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>www.password.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>eth.idpWarning.link1</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>https://www.password.ethz.ch/authentication/login_en.html</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>https://www.password.ethz.ch/</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>eth.idpWarning.link2</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>https://library.ethz.ch/en/borrowing-and-ordering/searching-for-finding-and-using-media/swisscovery.html#anleitung-registration-eth</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>https://library.ethz.ch/ausleihen-und-bestellen/medien-suchen-finden-und-nutzen/swisscovery.html#registrierung-eth</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.heading</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>Address changes</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>Adresse bearbeiten</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.ethMembers</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>Members of ETH</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>ETH-Angehörige</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.ethMembersIntro</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Change your address in 2 steps:</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>Ändern Sie Ihre Adresse in 2 Schritten:</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.ethMembersStep1</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>1. Change address:</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>1. Adresse ändern:</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.ethMembersStep2</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>2. Confirm address change:</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>2. Adressänderung bestätigen:</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.otherCustomers</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>Private individuals</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>Privatpersonen</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.otherCustomersIntro</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>Change your address here:</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>Ändern Sie Ihre Adresse hier:</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.ethMembersStep1Url</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>https://www.bi.id.ethz.ch/eAdressen/index_en.jsp</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>https://www.bi.id.ethz.ch/eAdressen</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.ethMembersStep2Url</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>https://eduid.ch</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>https://eduid.ch</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAdress.otherCustomersUrl</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>https://eduid.ch</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>https://eduid.ch</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>eth.bibNews.all</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>All news</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>Alle News</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>eth.geoRef.heading</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>Related Places</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>Verknüpfte Orte</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>eth.geoRef.entity</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>eth.provenance.heading</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>Provenance marks</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>Provenienzen</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>eth.provenance.entity</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>Provenienz</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>eth.provenance.date</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>Datierung:</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>eth.provenance.epicsLinkText</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>Provenance in E-Pics</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>Provenienz in E-Pics</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>eth.personCard.entity</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>eth.personCard.photo</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Photo of</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>Photo von</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>eth.personCard.licence</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>Licence for the picture see</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>Lizenz für das Bild siehe</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>eth.personCard.heading</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Related Persons</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>Verknüpfte Personen</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>eth.personCard.headingMore</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>More related Persons</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>Mehr Personen</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>eth.placePage.topics</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>Topics in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>Geografisches Schlagwort in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>eth.placePage.ethorama</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>Documents in ETHorama</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>Dokumente in ETHorama</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>eth.placePage.ethoramaTopics</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>ETHorama thematic collections</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>ETHorama Themensammlungen</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>eth.placePage.ethoramaRoutes</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>ETHorama historical travels</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>ETHorama Historische Reisen</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>eth.placePage.wikidata</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Links from Wikidata</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>Links from Wikidata</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>eth.placePage.maps</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>Historical maps</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>Historische Karten</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>eth.placePage.mapsList</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>Historical maps as list</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>Historische Karten als Liste</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46000.0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F46"/>
+  <autoFilter ref="A1:F85"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$104</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -95,7 +95,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.02734375" customWidth="true"/>
+    <col min="1" max="1" width="8.59375" customWidth="true"/>
     <col min="2" max="2" width="39.2421875" customWidth="true"/>
     <col min="3" max="3" width="255.0" customWidth="true"/>
     <col min="4" max="4" width="27.34375" customWidth="true"/>
@@ -2655,8 +2655,578 @@
         <v>46000.0</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.searchVariants</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Search variants in all data of the ETH Library</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>Suchvarianten in allen Daten der ETH-Bibliothek</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.results</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>results</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>Ergebnisse</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.authorityLinking</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>Authority data</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>Normdaten</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.researcherProfile</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>Researcher profiles</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>Forscherprofile</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.archives</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>Archives</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.metagrid</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>Metagrid</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>Metagrid</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.wikidata</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>Wikidata</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>Wikidata</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.prometheus</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>Prometheus</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>Prometheus</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.students</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Students (Wikidata)</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>Studenten (Wikidata)</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.teacher</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>Teachers (Wikidata)</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>Lehrer (Wikidata)</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.relatedGnd</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>Related persons from GND</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>Verbundene Personen nach GND</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.prometheusIntro1</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>Links from the</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>Links vom</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.prometheusIntro2</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>Aggregator of the</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>Aggregator des</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.prometheusIntro3</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>LMU Center for Digital Humanities</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>LMU Center for Digital Humanities</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.searchName</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>Search by name</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>Suche nach Namen</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.searchGnd</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Search by GND ID</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>Suche nach GND ID</t>
+        </is>
+      </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.searchGndBirth</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>Search by name and (GND ID or birthyear)</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>Suche nach Name und (GND ID oder Geburtsjahr)</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.born</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>Born:</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>Geboren:</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>eth.personPage.prometheusAll</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>All links from Prometheus</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>Alle Links von Prometheus</t>
+        </is>
+      </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>46001.0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F85"/>
+  <autoFilter ref="A1:F104"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$109</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -3225,8 +3225,158 @@
         <v>46001.0</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>eth.provenienzEraraLink.erara</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Source in e-rara</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>Quelle in e-rara</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>46003.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>eth.provenienzEraraLink.swisscovery</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>Details provenance mark</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>Details Provenienzvermerk</t>
+        </is>
+      </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>46003.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>eth.bibNews.heading</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>46006.0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>eth.gitHint.heading</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>important information</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>Wichtiger Hinweis</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>46006.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>eth.locationLink.website</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>Webseite</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>46006.0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F104"/>
+  <autoFilter ref="A1:F109"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>Online anschauen</t>
+          <t>Online ansehen</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45999.0</v>
+        <v>46006.0</v>
       </c>
     </row>
     <row r="49">

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$E$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$E$110</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -176,7 +176,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="4">
@@ -201,7 +201,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="5">
@@ -226,7 +226,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="6">
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="7">
@@ -276,7 +276,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="8">
@@ -301,7 +301,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="9">
@@ -326,7 +326,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="10">
@@ -351,7 +351,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="11">
@@ -376,7 +376,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="12">
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="13">
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="14">
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="15">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="16">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="17">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="19">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="20">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="21">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="22">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="23">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="24">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="25">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45978.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="26">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="27">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="28">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="29">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="30">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="31">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="32">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>46097.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="33">
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="34">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="35">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="36">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="37">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="38">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="39">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="40">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="41">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="42">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="43">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="44">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="45">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="46">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="47">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="48">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="49">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>45999.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="50">
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="51">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="52">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="53">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="54">
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="55">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="56">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="57">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="58">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="59">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="60">
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="61">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="62">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="63">
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="64">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="65">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="66">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="67">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="68">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="69">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="70">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="71">
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="72">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="73">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="74">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="75">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="76">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="77">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="78">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="79">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="80">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="81">
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="82">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="83">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="84">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="85">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>46000.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="86">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="87">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="88">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="89">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="90">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="91">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="92">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="93">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="94">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="95">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="96">
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="97">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="98">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="99">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="100">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="101">
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="102">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="103">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="104">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>46001.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="105">
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>46003.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="106">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>46003.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="107">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>46006.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="108">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>46006.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="109">
@@ -2826,11 +2826,36 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>46006.0</v>
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>eth.rapidoEthmemberHint.text</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>Please check in the upper ordering section if one of the libraries at ETH Zurich offers "Digitization" (free service).</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E109"/>
+  <autoFilter ref="A1:E110"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$E$120</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -97,10 +97,9 @@
   <cols>
     <col min="1" max="1" width="8.59375" customWidth="true"/>
     <col min="2" max="2" width="44.8125" customWidth="true"/>
-    <col min="3" max="3" width="68.75" customWidth="true"/>
-    <col min="4" max="4" width="68.75" customWidth="true"/>
-    <col min="5" max="5" width="34.00390625" customWidth="true"/>
-    <col min="6" max="6" width="13.20703125" customWidth="true"/>
+    <col min="3" max="3" width="255.0" customWidth="true"/>
+    <col min="4" max="4" width="27.34375" customWidth="true"/>
+    <col min="5" max="5" width="11.71875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -121,15 +120,10 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Translation-German</t>
+          <t>Updated By</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Updated By</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
@@ -153,16 +147,11 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Die Bibliothek Professur für Literatur- und Kulturwissenschaft befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; möglich.</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>45968.0</v>
       </c>
     </row>
     <row r="3">
@@ -183,16 +172,11 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach Voranmeldung bei &lt;a href="mailto:archiv@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="4">
@@ -213,16 +197,11 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="5">
@@ -243,16 +222,11 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="6">
@@ -273,16 +247,11 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="7">
@@ -303,16 +272,11 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="8">
@@ -333,16 +297,11 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Lizenzierte E-Ressourcen der ETH-Bibliothek sind über das ETH-Netzwerk oder</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="9">
@@ -363,16 +322,11 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>zugänglich.</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="10">
@@ -393,16 +347,11 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>https://unlimited.ethz.ch/help/network/vpn</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="11">
@@ -423,16 +372,11 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>VPN</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="12">
@@ -453,16 +397,11 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://ethz.ch/staffnet/de/anstellung-und-arbeit/arbeitsumfeld/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="13">
@@ -483,15 +422,10 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Die Bibliothek von ETH Diversity befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:diversity@ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; möglich.</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>46111.0</v>
       </c>
     </row>
@@ -513,16 +447,11 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Möchten Sie einen Scan eines Artikels oder Kapitels aus diesem Dokument bestellen? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan-Anfrage: MMS ID {{id}}"&gt;Schreiben Sie uns!&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="15">
@@ -543,16 +472,11 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://infozentrum.ethz.ch/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="16">
@@ -573,16 +497,11 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/archivieren-und-digitalisieren/archivieren/hochschularchiv-der-eth-zuerich.html" target="_blank" &gt;Hochschularchiv der ETH Zürich&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>46058.0</v>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>46108.0</v>
       </c>
     </row>
     <row r="17">
@@ -603,19 +522,14 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="18" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -633,19 +547,14 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="19" customHeight="true" ht="45.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -663,19 +572,14 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:mfa@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="20" customHeight="true" ht="45.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -693,19 +597,14 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="21" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -723,19 +622,14 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="22" customHeight="true" ht="45.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -753,19 +647,14 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Benutzung vor Ort nur nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="23" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -783,19 +672,14 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/de/bibliothek" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="24" customHeight="true" ht="45.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -813,19 +697,14 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="25" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -843,19 +722,14 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://afz.ethz.ch/recherche-archivbesuch/recherche/bibliothek.html" target="_blank" &gt;Archiv für Zeitgeschichte&lt;a&gt;</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -873,19 +747,14 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Metagrid-Links zeigen</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="27" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -903,19 +772,14 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Metagrid-Links ausblenden</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="28" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -933,19 +797,14 @@
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Artikel/Kapitel ist im swisscovery Network nicht vorhanden oder nicht bestellbar.</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="29" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -963,19 +822,14 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Bestellen Sie bitte via</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="30" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -993,19 +847,14 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="31" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1023,19 +872,14 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Fernleihe</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="32" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1053,19 +897,14 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/bestellformulare/fernleihe-kopien-bestellen.html</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>46097.0</v>
-      </c>
-    </row>
-    <row r="33" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1083,19 +922,14 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>Print-Exemplar in ETH swisscovery</t>
-        </is>
-      </c>
-      <c r="E33" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="34" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1113,19 +947,14 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Online-Exemplar in ETH swisscovery (e-rara)</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="35" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1143,19 +972,14 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>Georeferenziertes Online-Exemplar in ETH swisscovery (e-maps)</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="36" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1173,19 +997,14 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>GeoTIFF via e-maps</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="37" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1203,19 +1022,14 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>Print-Exemplar in ETH swisscovery</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="38" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1233,19 +1047,14 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>Online-Exemplar in ETH swisscovery</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="39" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1263,19 +1072,14 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>Inhaltsverzeichnis der DNB zu</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="40" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1293,19 +1097,14 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>Inhaltstext der DNB zu</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="41" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1323,19 +1122,14 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>Passwortgeschützter Zugang. Nur für Mitglieder der ETH Zürich zugänglich.</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="42" customHeight="true" ht="45.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1353,19 +1147,14 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Sie müssen sich mit Ihrer ETH Zürich E-Mail-Adresse unter „Anmelden” registrieren. Der Zugriff auf diese Quelle ist aufgrund von Lizenzbeschränkungen auf die Domain ethz.ch eingeschränkt.</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="43" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1383,19 +1172,14 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>Wählen Sie im Webarchiv ein Jahr und ein blau markiertes Datum, um die archivierte Website aufzurufen.</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="44" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1413,19 +1197,14 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>Link zum Webarchiv</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="45" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1443,19 +1222,14 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>Zugriffsproblem melden</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="46" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1473,19 +1247,14 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>Zugriffsproblem per E-Mail melden</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="47" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1503,19 +1272,14 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>Noch nicht registriert?</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="48" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1533,19 +1297,14 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>Online ansehen</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="49" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1563,19 +1322,14 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>Suche nach “{{ search }}” in Open Knowledge Maps:</t>
-        </is>
-      </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="50" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1593,19 +1347,14 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>ETH swisscovery</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="51" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1623,19 +1372,14 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfen Sie Ihre SWITCH edu-ID mit Ihrem ETH-Benutzerkonto in</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="52" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1653,19 +1397,14 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>, um von den Vorteilen für ETH-Angehörige zu profitieren.</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="53" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1683,19 +1422,14 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>Anleitung</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="54" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1713,19 +1447,14 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>www.password.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="55" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1743,19 +1472,14 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>https://www.password.ethz.ch/</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="56" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1773,19 +1497,14 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/ausleihen-und-bestellen/medien-suchen-finden-und-nutzen/swisscovery.html#registrierung-eth</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="57" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1803,19 +1522,14 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>Adresse bearbeiten</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="58" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1833,19 +1547,14 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>ETH-Angehörige</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="59" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1863,19 +1572,14 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>Ändern Sie Ihre Adresse in 2 Schritten:</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="60" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1893,19 +1597,14 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>1. Adresse ändern:</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="61" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1923,19 +1622,14 @@
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>2. Adressänderung bestätigen:</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="62" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1953,19 +1647,14 @@
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>Privatpersonen</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="63" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1983,19 +1672,14 @@
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>Ändern Sie Ihre Adresse hier:</t>
-        </is>
-      </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="64" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2013,19 +1697,14 @@
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>https://idapps.ethz.ch/contact-data/</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
         <v>46141.0</v>
       </c>
     </row>
-    <row r="65" customHeight="true" ht="15.0">
+    <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2043,49 +1722,39 @@
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>eth.changeAddress.otherCustomersUrl</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
           <t>https://eduid.ch</t>
         </is>
       </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="66" customHeight="true" ht="15.0">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>eth.changeAddress.otherCustomersUrl</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>https://eduid.ch</t>
-        </is>
-      </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>https://eduid.ch</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="67" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2103,19 +1772,14 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>Alle News</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="68" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2133,19 +1797,14 @@
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfte Orte</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="69" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2163,19 +1822,14 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="70" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2193,19 +1847,14 @@
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>Provenienzen</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="71" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2223,19 +1872,14 @@
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>Provenienz</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="72" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2253,19 +1897,14 @@
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>Datierung:</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="73" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2283,19 +1922,14 @@
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>Provenienz in E-Pics</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="74" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2313,19 +1947,14 @@
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="75" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2343,19 +1972,14 @@
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>Photo von</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="76" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2373,19 +1997,14 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>Lizenz für das Bild siehe</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="77" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2403,19 +2022,14 @@
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfte Personen</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="78" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2433,19 +2047,14 @@
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>Mehr Personen</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="79" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2463,19 +2072,14 @@
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>Geografisches Schlagwort in ETH swisscovery</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="80" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2493,19 +2097,14 @@
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>Dokumente in ETHorama</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="81" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2523,19 +2122,14 @@
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>ETHorama Themensammlungen</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="82" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2553,19 +2147,14 @@
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>ETHorama Historische Reisen</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="83" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2583,19 +2172,14 @@
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>Links from Wikidata</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="84" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2613,19 +2197,14 @@
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>Historische Karten</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="85" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2643,19 +2222,14 @@
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>Historische Karten als Liste</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="86" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2673,19 +2247,14 @@
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>Suchvarianten in allen Daten der ETH-Bibliothek</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="87" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2703,19 +2272,14 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>Ergebnisse</t>
-        </is>
-      </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="88" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2733,19 +2297,14 @@
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>Normdaten</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="89" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2763,19 +2322,14 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>Forscherprofile</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="90" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2793,19 +2347,14 @@
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>Archive</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="91" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2823,19 +2372,14 @@
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>Metagrid</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="92" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2853,19 +2397,14 @@
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>Wikidata</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="93" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2883,19 +2422,14 @@
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>Prometheus</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="94" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2913,19 +2447,14 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>Studenten (Wikidata)</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="95" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2943,19 +2472,14 @@
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>Lehrer (Wikidata)</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="96" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2973,19 +2497,14 @@
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>Verbundene Personen nach GND</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="97" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3003,19 +2522,14 @@
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>Links vom</t>
-        </is>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="98" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3033,19 +2547,14 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Aggregator des</t>
-        </is>
-      </c>
-      <c r="E98" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="99" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3063,19 +2572,14 @@
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>LMU Center for Digital Humanities</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="100" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3093,19 +2597,14 @@
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>Suche nach Namen</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="101" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3123,19 +2622,14 @@
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>Suche nach GND ID</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="102" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3153,19 +2647,14 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>Suche nach Name und (GND ID oder Geburtsjahr)</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="103" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3183,19 +2672,14 @@
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>Geboren:</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="104" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3213,19 +2697,14 @@
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>Alle Links von Prometheus</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="105" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3243,19 +2722,14 @@
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>Quelle in e-rara</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="106" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3273,19 +2747,14 @@
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>Details Provenienzvermerk</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="107" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3303,19 +2772,14 @@
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>News</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="108" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3333,19 +2797,14 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>Wichtiger Hinweis</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="109" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3363,19 +2822,14 @@
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>Webseite</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>46058.0</v>
-      </c>
-    </row>
-    <row r="110" customHeight="true" ht="30.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3393,19 +2847,14 @@
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>Überprüfen Sie bitte im oberen Bestellbereich, ob eine Bibliothek der ETH Zürich "Digitalisierung" anbietet (kostenloser Service).</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>46108.0</v>
-      </c>
-    </row>
-    <row r="111" customHeight="true" ht="15.0">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>46108.0</v>
+      </c>
+    </row>
+    <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3423,19 +2872,14 @@
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>Print-Exemplar in TMI Research</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="n">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
         <v>46113.0</v>
       </c>
     </row>
-    <row r="112" customHeight="true" ht="15.0">
+    <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3453,19 +2897,14 @@
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>Online-Exemplar in TMI Research</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="n">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
         <v>46113.0</v>
       </c>
     </row>
-    <row r="113" customHeight="true" ht="15.0">
+    <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3483,19 +2922,14 @@
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>TMI Research</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="n">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
         <v>46113.0</v>
       </c>
     </row>
-    <row r="114" customHeight="true" ht="30.0">
+    <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3513,19 +2947,14 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00 (kostenlos an ETH-Institutsadresse)</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="n">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
         <v>46141.0</v>
       </c>
     </row>
-    <row r="115" customHeight="true" ht="30.0">
+    <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3543,19 +2972,14 @@
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>Normale Gebühr: CHF 5.00&lt;br&gt;ETH-Mitarbeitende: kostenlos&lt;br&gt;Alle Studierende: CHF 2.50&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="n">
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
         <v>46141.0</v>
       </c>
     </row>
-    <row r="116" customHeight="true" ht="15.0">
+    <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3563,60 +2987,125 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
+          <t>tmi.getit.E73BI</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;Can be used in the reading room of the Thomas Mann Archives subject to prior appointment.&lt;/div&gt; &lt;div&gt;Contact: &lt;a href="mailto:tma@library.ethz.ch?subject=Appointment for: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH&amp;docid=alma{{id}}"&gt;         &lt;span&gt;More Informations in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>46150.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
           <t>eth.requestHint.digitizationOtherLibrary</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>Normal fee: CHF 5.00&lt;br&gt;Commercial clients: CHF 25.00</t>
         </is>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>Normale Gebühr: CHF 5.00&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="n">
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
         <v>46142.0</v>
       </c>
     </row>
-    <row r="117" customHeight="true" ht="15.0">
-      <c r="A117" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>tmi.getit.tmhla</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &lt;div&gt;       &lt;span&gt;Not loanable.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Can be used in the library of the Thomas Mann House by prior appointment. Please contact&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Request about: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;  </t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>46150.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
         <is>
           <t>eth.requestHint.requestOtherLibrary</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00</t>
         </is>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="n">
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
         <v>46142.0</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>tmi.getit.luebeck</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     &lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailed information in the online database of the Buddenbrookhaus     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Not possible to order.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digital copies can be requested from Buddenbrookhaus (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Request about: {{callNumber}}"&gt;Contact&lt;/a&gt; ).     &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>46150.0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F117"/>
+  <autoFilter ref="A1:E120"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$E$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$122</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -99,7 +99,8 @@
     <col min="2" max="2" width="44.8125" customWidth="true"/>
     <col min="3" max="3" width="255.0" customWidth="true"/>
     <col min="4" max="4" width="27.34375" customWidth="true"/>
-    <col min="5" max="5" width="11.71875" customWidth="true"/>
+    <col min="5" max="5" width="27.34375" customWidth="true"/>
+    <col min="6" max="6" width="11.71875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -120,10 +121,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Translation-German</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Updated By</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
@@ -147,11 +153,16 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>45968.0</v>
+          <t>Die Bibliothek Professur für Literatur- und Kulturwissenschaft befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; möglich.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="3">
@@ -172,11 +183,16 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach Voranmeldung bei &lt;a href="mailto:archiv@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="4">
@@ -197,11 +213,16 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="5">
@@ -222,11 +243,16 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="6">
@@ -247,11 +273,16 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="7">
@@ -272,11 +303,16 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="8">
@@ -297,11 +333,16 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>46108.0</v>
+          <t>Lizenzierte E-Ressourcen der ETH-Bibliothek sind über das ETH-Netzwerk oder</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="9">
@@ -322,11 +363,16 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>46108.0</v>
+          <t>zugänglich.</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="10">
@@ -347,11 +393,16 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>46108.0</v>
+          <t>https://unlimited.ethz.ch/help/network/vpn</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="11">
@@ -372,11 +423,16 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>46108.0</v>
+          <t>VPN</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="12">
@@ -397,11 +453,16 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://ethz.ch/staffnet/de/anstellung-und-arbeit/arbeitsumfeld/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="13">
@@ -422,10 +483,15 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
+          <t>Die Bibliothek von ETH Diversity befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:diversity@ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; möglich.</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>46111.0</v>
       </c>
     </row>
@@ -447,11 +513,16 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>46108.0</v>
+          <t>Möchten Sie einen Scan eines Artikels oder Kapitels aus diesem Dokument bestellen? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan-Anfrage: MMS ID {{id}}"&gt;Schreiben Sie uns!&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="15">
@@ -472,11 +543,16 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://infozentrum.ethz.ch/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="16">
@@ -497,11 +573,16 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://library.ethz.ch/archivieren-und-digitalisieren/archivieren/hochschularchiv-der-eth-zuerich.html" target="_blank" &gt;Hochschularchiv der ETH Zürich&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="17">
@@ -522,11 +603,16 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="18">
@@ -547,11 +633,16 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="19">
@@ -572,11 +663,16 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>46108.0</v>
+          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:mfa@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="20">
@@ -597,11 +693,16 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>46108.0</v>
+          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="21">
@@ -622,11 +723,16 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="22">
@@ -647,11 +753,16 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>46108.0</v>
+          <t>Benutzung vor Ort nur nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="23">
@@ -672,11 +783,16 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/de/bibliothek" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="24">
@@ -697,11 +813,16 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="25">
@@ -722,11 +843,16 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>46108.0</v>
+          <t>&lt;a href="https://afz.ethz.ch/recherche-archivbesuch/recherche/bibliothek.html" target="_blank" &gt;Archiv für Zeitgeschichte&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="26">
@@ -747,11 +873,16 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>46108.0</v>
+          <t>Metagrid-Links zeigen</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="27">
@@ -772,11 +903,16 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>46108.0</v>
+          <t>Metagrid-Links ausblenden</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="28">
@@ -797,11 +933,16 @@
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>46108.0</v>
+          <t>Artikel/Kapitel ist im swisscovery Network nicht vorhanden oder nicht bestellbar.</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="29">
@@ -822,11 +963,16 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>46108.0</v>
+          <t>Bestellen Sie bitte via</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="30">
@@ -847,11 +993,16 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>46108.0</v>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="31">
@@ -872,11 +1023,16 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>46108.0</v>
+          <t>Fernleihe</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="32">
@@ -897,11 +1053,16 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>46108.0</v>
+          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/bestellformulare/fernleihe-kopien-bestellen.html</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>46097.0</v>
       </c>
     </row>
     <row r="33">
@@ -922,11 +1083,16 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>46108.0</v>
+          <t>Print-Exemplar in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="34">
@@ -947,11 +1113,16 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>46108.0</v>
+          <t>Online-Exemplar in ETH swisscovery (e-rara)</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="35">
@@ -972,11 +1143,16 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>46108.0</v>
+          <t>Georeferenziertes Online-Exemplar in ETH swisscovery (e-maps)</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="36">
@@ -997,11 +1173,16 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>46108.0</v>
+          <t>GeoTIFF via e-maps</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="37">
@@ -1022,11 +1203,16 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>46108.0</v>
+          <t>Print-Exemplar in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="38">
@@ -1047,11 +1233,16 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>46108.0</v>
+          <t>Online-Exemplar in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="39">
@@ -1072,11 +1263,16 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>46108.0</v>
+          <t>Inhaltsverzeichnis der DNB zu</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="40">
@@ -1097,11 +1293,16 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>46108.0</v>
+          <t>Inhaltstext der DNB zu</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="41">
@@ -1122,11 +1323,16 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>46108.0</v>
+          <t>Passwortgeschützter Zugang. Nur für Mitglieder der ETH Zürich zugänglich.</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="42">
@@ -1147,11 +1353,16 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>46108.0</v>
+          <t>Sie müssen sich mit Ihrer ETH Zürich E-Mail-Adresse unter „Anmelden” registrieren. Der Zugriff auf diese Quelle ist aufgrund von Lizenzbeschränkungen auf die Domain ethz.ch eingeschränkt.</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="43">
@@ -1172,11 +1383,16 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>46108.0</v>
+          <t>Wählen Sie im Webarchiv ein Jahr und ein blau markiertes Datum, um die archivierte Website aufzurufen.</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="44">
@@ -1197,11 +1413,16 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>46108.0</v>
+          <t>Link zum Webarchiv</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="45">
@@ -1222,11 +1443,16 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>46108.0</v>
+          <t>Zugriffsproblem melden</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="46">
@@ -1247,11 +1473,16 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>46108.0</v>
+          <t>Zugriffsproblem per E-Mail melden</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="47">
@@ -1272,11 +1503,16 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>46108.0</v>
+          <t>Noch nicht registriert?</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="48">
@@ -1297,11 +1533,16 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>46108.0</v>
+          <t>Online ansehen</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="49">
@@ -1322,11 +1563,16 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>46108.0</v>
+          <t>Suche nach “{{ search }}” in Open Knowledge Maps:</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="50">
@@ -1347,11 +1593,16 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>46108.0</v>
+          <t>ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="51">
@@ -1372,11 +1623,16 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>46108.0</v>
+          <t>Verknüpfen Sie Ihre SWITCH edu-ID mit Ihrem ETH-Benutzerkonto in</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="52">
@@ -1397,11 +1653,16 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>46108.0</v>
+          <t>, um von den Vorteilen für ETH-Angehörige zu profitieren.</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="53">
@@ -1422,11 +1683,16 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>46108.0</v>
+          <t>Anleitung</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="54">
@@ -1447,11 +1713,16 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>46108.0</v>
+          <t>www.password.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="55">
@@ -1472,11 +1743,16 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>46108.0</v>
+          <t>https://www.password.ethz.ch/</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="56">
@@ -1497,11 +1773,16 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>46108.0</v>
+          <t>https://library.ethz.ch/ausleihen-und-bestellen/medien-suchen-finden-und-nutzen/swisscovery.html#registrierung-eth</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="57">
@@ -1522,11 +1803,16 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>46108.0</v>
+          <t>Adresse bearbeiten</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="58">
@@ -1547,11 +1833,16 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>46108.0</v>
+          <t>ETH-Angehörige</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="59">
@@ -1572,11 +1863,16 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>46108.0</v>
+          <t>Ändern Sie Ihre Adresse in 2 Schritten:</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="60">
@@ -1597,11 +1893,16 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>46108.0</v>
+          <t>1. Adresse ändern:</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="61">
@@ -1622,11 +1923,16 @@
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>46108.0</v>
+          <t>2. Adressänderung bestätigen:</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="62">
@@ -1647,11 +1953,16 @@
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>46108.0</v>
+          <t>Privatpersonen</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="63">
@@ -1672,11 +1983,16 @@
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>46108.0</v>
+          <t>Ändern Sie Ihre Adresse hier:</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="64">
@@ -1697,10 +2013,15 @@
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="n">
+          <t>https://idapps.ethz.ch/contact-data/</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
         <v>46141.0</v>
       </c>
     </row>
@@ -1722,11 +2043,16 @@
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>46108.0</v>
+          <t>https://eduid.ch</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="66">
@@ -1747,11 +2073,16 @@
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>46108.0</v>
+          <t>https://eduid.ch</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="67">
@@ -1772,11 +2103,16 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>46108.0</v>
+          <t>Alle News</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="68">
@@ -1797,11 +2133,16 @@
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>46108.0</v>
+          <t>Verknüpfte Orte</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="69">
@@ -1822,11 +2163,16 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>46108.0</v>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="70">
@@ -1847,11 +2193,16 @@
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>46108.0</v>
+          <t>Provenienzen</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="71">
@@ -1872,11 +2223,16 @@
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>46108.0</v>
+          <t>Provenienz</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="72">
@@ -1897,11 +2253,16 @@
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>46108.0</v>
+          <t>Datierung:</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="73">
@@ -1922,11 +2283,16 @@
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>46108.0</v>
+          <t>Provenienz in E-Pics</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="74">
@@ -1947,11 +2313,16 @@
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>46108.0</v>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="75">
@@ -1972,11 +2343,16 @@
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>46108.0</v>
+          <t>Photo von</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="76">
@@ -1997,11 +2373,16 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>46108.0</v>
+          <t>Lizenz für das Bild siehe</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="77">
@@ -2022,11 +2403,16 @@
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>46108.0</v>
+          <t>Verknüpfte Personen</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="78">
@@ -2047,11 +2433,16 @@
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>46108.0</v>
+          <t>Mehr Personen</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="79">
@@ -2072,11 +2463,16 @@
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>46108.0</v>
+          <t>Geografisches Schlagwort in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="80">
@@ -2097,11 +2493,16 @@
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>46108.0</v>
+          <t>Dokumente in ETHorama</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="81">
@@ -2122,11 +2523,16 @@
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>46108.0</v>
+          <t>ETHorama Themensammlungen</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="82">
@@ -2147,11 +2553,16 @@
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>46108.0</v>
+          <t>ETHorama Historische Reisen</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="83">
@@ -2172,11 +2583,16 @@
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>46108.0</v>
+          <t>Links from Wikidata</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="84">
@@ -2197,11 +2613,16 @@
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>46108.0</v>
+          <t>Historische Karten</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="85">
@@ -2222,11 +2643,16 @@
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>46108.0</v>
+          <t>Historische Karten als Liste</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="86">
@@ -2247,11 +2673,16 @@
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>46108.0</v>
+          <t>Suchvarianten in allen Daten der ETH-Bibliothek</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="87">
@@ -2272,11 +2703,16 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>46108.0</v>
+          <t>Ergebnisse</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="88">
@@ -2297,11 +2733,16 @@
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>46108.0</v>
+          <t>Normdaten</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="89">
@@ -2322,11 +2763,16 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>46108.0</v>
+          <t>Forscherprofile</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="90">
@@ -2347,11 +2793,16 @@
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>46108.0</v>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="91">
@@ -2372,11 +2823,16 @@
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>46108.0</v>
+          <t>Metagrid</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="92">
@@ -2397,11 +2853,16 @@
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>46108.0</v>
+          <t>Wikidata</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="93">
@@ -2422,11 +2883,16 @@
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>46108.0</v>
+          <t>Prometheus</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="94">
@@ -2447,11 +2913,16 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>46108.0</v>
+          <t>Studenten (Wikidata)</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="95">
@@ -2472,11 +2943,16 @@
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>46108.0</v>
+          <t>Lehrer (Wikidata)</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="96">
@@ -2497,11 +2973,16 @@
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>46108.0</v>
+          <t>Verbundene Personen nach GND</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="97">
@@ -2522,11 +3003,16 @@
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>46108.0</v>
+          <t>Links vom</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="98">
@@ -2547,11 +3033,16 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>46108.0</v>
+          <t>Aggregator des</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="99">
@@ -2572,11 +3063,16 @@
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>46108.0</v>
+          <t>LMU Center for Digital Humanities</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="100">
@@ -2597,11 +3093,16 @@
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>46108.0</v>
+          <t>Suche nach Namen</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="101">
@@ -2622,11 +3123,16 @@
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>46108.0</v>
+          <t>Suche nach GND ID</t>
+        </is>
+      </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="102">
@@ -2647,11 +3153,16 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>46108.0</v>
+          <t>Suche nach Name und (GND ID oder Geburtsjahr)</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="103">
@@ -2672,11 +3183,16 @@
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>46108.0</v>
+          <t>Geboren:</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="104">
@@ -2697,11 +3213,16 @@
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>46108.0</v>
+          <t>Alle Links von Prometheus</t>
+        </is>
+      </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="105">
@@ -2722,11 +3243,16 @@
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>46108.0</v>
+          <t>Quelle in e-rara</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="106">
@@ -2747,11 +3273,16 @@
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>46108.0</v>
+          <t>Details Provenienzvermerk</t>
+        </is>
+      </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="107">
@@ -2772,11 +3303,16 @@
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>46108.0</v>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="108">
@@ -2797,11 +3333,16 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>46108.0</v>
+          <t>Wichtiger Hinweis</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="109">
@@ -2822,11 +3363,16 @@
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>46108.0</v>
+          <t>Webseite</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>46058.0</v>
       </c>
     </row>
     <row r="110">
@@ -2847,10 +3393,15 @@
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="n">
+          <t>Überprüfen Sie bitte im oberen Bestellbereich, ob eine Bibliothek der ETH Zürich "Digitalisierung" anbietet (kostenloser Service).</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
         <v>46108.0</v>
       </c>
     </row>
@@ -2872,10 +3423,15 @@
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="n">
+          <t>Print-Exemplar in TMI Research</t>
+        </is>
+      </c>
+      <c r="E111" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
         <v>46113.0</v>
       </c>
     </row>
@@ -2897,10 +3453,15 @@
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="n">
+          <t>Online-Exemplar in TMI Research</t>
+        </is>
+      </c>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
         <v>46113.0</v>
       </c>
     </row>
@@ -2922,10 +3483,15 @@
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="n">
+          <t>TMI Research</t>
+        </is>
+      </c>
+      <c r="E113" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
         <v>46113.0</v>
       </c>
     </row>
@@ -2947,10 +3513,15 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="n">
+          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00 (kostenlos an ETH-Institutsadresse)</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
         <v>46141.0</v>
       </c>
     </row>
@@ -2972,10 +3543,15 @@
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="n">
+          <t>Normale Gebühr: CHF 5.00&lt;br&gt;ETH-Mitarbeitende: kostenlos&lt;br&gt;Alle Studierende: CHF 2.50&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
+        </is>
+      </c>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
         <v>46141.0</v>
       </c>
     </row>
@@ -2997,11 +3573,16 @@
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>46150.0</v>
+          <t>&lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;Benutzung im Lesesaal des Thomas-Mann-Archivs auf Voranmeldung.&lt;/div&gt; &lt;div&gt;Kontakt: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH&amp;docid=alma{{id}}"&gt;         &lt;span&gt;Mehr Informationen in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="E116" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>46149.0</v>
       </c>
     </row>
     <row r="117">
@@ -3022,10 +3603,15 @@
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="n">
+          <t>Normale Gebühr: CHF 5.00&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
+        </is>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
         <v>46142.0</v>
       </c>
     </row>
@@ -3042,16 +3628,21 @@
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &lt;div&gt;       &lt;span&gt;Not loanable.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Can be used in the library of the Thomas Mann House by prior appointment. Please contact&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Request about: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;  </t>
+          <t>&lt;div&gt;       &lt;span&gt;Not loanable.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Can be used in the library of the Thomas Mann House by prior appointment. Please contact&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Request about: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>46150.0</v>
+          <t>&lt;div&gt;  &lt;span&gt;Nicht ausleihbar.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Benutzung nach vorheriger Anmeldung in der Bibliothek des Thomas-Mann-Hauses. Bitte kontaktieren Sie&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Anfrage zu: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>46149.0</v>
       </c>
     </row>
     <row r="119">
@@ -3072,10 +3663,15 @@
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="n">
+          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00</t>
+        </is>
+      </c>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
         <v>46142.0</v>
       </c>
     </row>
@@ -3092,20 +3688,85 @@
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">     &lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailed information in the online database of the Buddenbrookhaus     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Not possible to order.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digital copies can be requested from Buddenbrookhaus (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Request about: {{callNumber}}"&gt;Contact&lt;/a&gt; ).     &lt;/div&gt;</t>
+          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailed information in the online database of the Buddenbrookhaus     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Not possible to order.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digital copies can be requested from Buddenbrookhaus (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Request about: {{callNumber}}"&gt;Contact&lt;/a&gt; ).     &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>46150.0</v>
+          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailinformationen in der Online-Datenbank des Buddenbrookhauses     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Keine Bestellung möglich.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digitalisate können beim Buddenbrookhaus angefragt werden (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Anfrage zu: {{callNumber}}"&gt;Kontakt&lt;/a&gt; ).     &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>46149.0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>tmi.viewit.monacensia</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;Detailed information in the Kalliope Union Catalog (metadata only) &lt;/a&gt; &lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;     Archival materials can be viewed on site at the Monacensia im Hildebrandhaus (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Request digitized copy with signature: {{callNumber}}"&gt;       Contact     &lt;/a&gt; ). &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;     Detailinformationen in der Online-Datenbank der Monacensia im Hildebrandhaus (nur Metadaten) &lt;/a&gt; &lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;     Archivalien können vor Ort in der Monacensia im Hildebrandhaus eingesehen werden (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Anfrage Digitalisat mit Signatur "{{callNumber}}""&gt;       Kontakt     &lt;/a&gt; ). &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>46155.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>tmi.viewit.monacensia.heading</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>Zugang</t>
+        </is>
+      </c>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>46155.0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E120"/>
+  <autoFilter ref="A1:F122"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$129</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -96,7 +96,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="8.59375" customWidth="true"/>
-    <col min="2" max="2" width="44.8125" customWidth="true"/>
+    <col min="2" max="2" width="59.34765625" customWidth="true"/>
     <col min="3" max="3" width="255.0" customWidth="true"/>
     <col min="4" max="4" width="27.34375" customWidth="true"/>
     <col min="5" max="5" width="27.34375" customWidth="true"/>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/en/borrowing-and-ordering/searching-for-finding-and-using-media/swisscovery.html#anleitung-registration-eth</t>
+          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/frequently-asked-questions.html#eth-card-as-user-id</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/ausleihen-und-bestellen/medien-suchen-finden-und-nutzen/swisscovery.html#registrierung-eth</t>
+          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/faq.html#eth-karte-als-benutzungsausweis</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>46058.0</v>
+        <v>46163.0</v>
       </c>
     </row>
     <row r="57">
@@ -3765,8 +3765,218 @@
         <v>46155.0</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>41SLSP_ETH:TMI_NDE.nde.landing.header</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>NOT_DEFINED</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>NOT_DEFINED</t>
+        </is>
+      </c>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>46164.0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>eth.onlineProblem.mail</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>almakb@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t>almakb@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="E124" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>46169.0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>eth.topbarMessage.message</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>NOT_DEFINED</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>NOT_DEFINED</t>
+        </is>
+      </c>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>46178.0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>eth.topbarMessage.heading</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>Important information</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>Wichtiger Hinweis</t>
+        </is>
+      </c>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>46176.0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>eth.topbarMessage.message.41SLSP_ETH:ETH_CUSTOMIZING</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>ETH:✨Bücherbestellungen unter 'Weitere Bestelloptionen' momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>Testen Sie die Beta-Version des neuen KI-gestützten Research Assistant!  &lt;a href=\"https://library.ethz.ch/en/searching-and-using/research-assistant.html\" target=\"_blank\"&gt;Learn more&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>46177.0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>tmi.topbarMessage.message</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>TMI EN:✨das und das momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>TMI DE:✨das und das  nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>46178.0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>tmi.topbarMessage.heading</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>Important information</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>Wichtiger Hinweis</t>
+        </is>
+      </c>
+      <c r="E129" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46178.0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F122"/>
+  <autoFilter ref="A1:F129"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$132</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -143,26 +143,26 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E06.E06LI</t>
+          <t>slsp.locationLink.default</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>The library Chair for Literature and Cultural Studies is &lt;strong&gt;not&lt;/strong&gt; located at GESS Library.&lt;br&gt;&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; possible.</t>
+          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Die Bibliothek Professur für Literatur- und Kulturwissenschaft befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; möglich.</t>
+          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46058.0</v>
+        <v>46188.0</v>
       </c>
     </row>
     <row r="3">
@@ -173,17 +173,17 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E01.AETH</t>
+          <t>eth.locationHint.E06.E06LI</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;On-site use&lt;/strong&gt; only after appointment with &lt;a href="mailto:archiv@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
+          <t>The library Chair for Literature and Cultural Studies is &lt;strong&gt;not&lt;/strong&gt; located at GESS Library.&lt;br&gt;&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; possible.</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach Voranmeldung bei &lt;a href="mailto:archiv@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
+          <t>Die Bibliothek Professur für Literatur- und Kulturwissenschaft befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; möglich.</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -203,17 +203,17 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.default</t>
+          <t>eth.locationHint.E01.AETH</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
+          <t>&lt;strong&gt;On-site use&lt;/strong&gt; only after appointment with &lt;a href="mailto:archiv@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
+          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach Voranmeldung bei &lt;a href="mailto:archiv@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -233,17 +233,17 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E01</t>
+          <t>eth.locationLink.default</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
+          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
+          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -263,17 +263,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E03</t>
+          <t>eth.locationLink.E01</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -293,17 +293,17 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E06.E06LI</t>
+          <t>eth.locationLink.E03</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -323,17 +323,17 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>eth.offcampusWarning.text1</t>
+          <t>eth.locationLink.E06.E06LI</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>ETH Library’s licensed e-resources are accessible via the ETH network or</t>
+          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Lizenzierte E-Ressourcen der ETH-Bibliothek sind über das ETH-Netzwerk oder</t>
+          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -353,17 +353,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>eth.offcampusWarning.text2</t>
+          <t>eth.offcampusWarning.text1</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>ETH Library’s licensed e-resources are accessible via the ETH network or</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>zugänglich.</t>
+          <t>Lizenzierte E-Ressourcen der ETH-Bibliothek sind über das ETH-Netzwerk oder</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -383,17 +383,17 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>eth.offcampusWarning.url</t>
+          <t>eth.offcampusWarning.text2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>https://unlimited.ethz.ch/en/help/network/vpn</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>https://unlimited.ethz.ch/help/network/vpn</t>
+          <t>zugänglich.</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -413,17 +413,17 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>eth.offcampusWarning.linktext</t>
+          <t>eth.offcampusWarning.url</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>https://unlimited.ethz.ch/en/help/network/vpn</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>https://unlimited.ethz.ch/help/network/vpn</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -443,17 +443,17 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E06.E06EQ</t>
+          <t>eth.offcampusWarning.linktext</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://ethz.ch/staffnet/en/employment-and-work/working-environment/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://ethz.ch/staffnet/de/anstellung-und-arbeit/arbeitsumfeld/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E06.E06EQ</t>
+          <t>eth.locationLink.E06.E06EQ</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>The library of ETH Diversity is &lt;strong&gt;not&lt;/strong&gt; located at GESS Library.&lt;br&gt;&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:diversity@ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; possible.</t>
+          <t>&lt;a href="https://ethz.ch/staffnet/en/employment-and-work/working-environment/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Die Bibliothek von ETH Diversity befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:diversity@ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; möglich.</t>
+          <t>&lt;a href="https://ethz.ch/staffnet/de/anstellung-und-arbeit/arbeitsumfeld/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46111.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="14">
@@ -503,17 +503,17 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E33</t>
+          <t>eth.locationHint.E06.E06EQ</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Would you like to order a scan of an article or a chapter from this document? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan Request: MMS ID {{id}}"&gt;Write to us!&lt;/a&gt;</t>
+          <t>The library of ETH Diversity is &lt;strong&gt;not&lt;/strong&gt; located at GESS Library.&lt;br&gt;&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:diversity@ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; possible.</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Möchten Sie einen Scan eines Artikels oder Kapitels aus diesem Dokument bestellen? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan-Anfrage: MMS ID {{id}}"&gt;Schreiben Sie uns!&lt;/a&gt;</t>
+          <t>Die Bibliothek von ETH Diversity befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:diversity@ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; möglich.</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>46058.0</v>
+        <v>46111.0</v>
       </c>
     </row>
     <row r="15">
@@ -533,17 +533,17 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E33</t>
+          <t>eth.locationHint.E33</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://infozentrum.ethz.ch/en/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
+          <t>Would you like to order a scan of an article or a chapter from this document? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan Request: MMS ID {{id}}"&gt;Write to us!&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://infozentrum.ethz.ch/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
+          <t>Möchten Sie einen Scan eines Artikels oder Kapitels aus diesem Dokument bestellen? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan-Anfrage: MMS ID {{id}}"&gt;Schreiben Sie uns!&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E01.AETH</t>
+          <t>eth.locationLink.E33</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/en/archiving-and-digitising/archiving/eth-zurich-university-archives.html" target="_blank" &gt;ETH Zurich University Archives&lt;a&gt;</t>
+          <t>&lt;a href="https://infozentrum.ethz.ch/en/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/archivieren-und-digitalisieren/archivieren/hochschularchiv-der-eth-zuerich.html" target="_blank" &gt;Hochschularchiv der ETH Zürich&lt;a&gt;</t>
+          <t>&lt;a href="https://infozentrum.ethz.ch/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E73.E73MF</t>
+          <t>eth.locationLink.E01.AETH</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/en/archiving-and-digitising/archiving/eth-zurich-university-archives.html" target="_blank" &gt;ETH Zurich University Archives&lt;a&gt;</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/archivieren-und-digitalisieren/archivieren/hochschularchiv-der-eth-zuerich.html" target="_blank" &gt;Hochschularchiv der ETH Zürich&lt;a&gt;</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E73.E73BI</t>
+          <t>eth.locationLink.E73.E73MF</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -653,17 +653,17 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E73.E73MF</t>
+          <t>eth.locationLink.E73.E73BI</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Use only on site. Information can be obtained by e-mail to:  &lt;a href="mailto:mfa@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:mfa@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E73.E73BI</t>
+          <t>eth.locationHint.E73.E73MF</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>Use only on site. Information can be obtained by e-mail to:  &lt;a href="mailto:tma@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt;</t>
+          <t>Use only on site. Information can be obtained by e-mail to:  &lt;a href="mailto:mfa@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt;</t>
+          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:mfa@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E76</t>
+          <t>eth.locationHint.E73.E73BI</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
+          <t>Use only on site. Information can be obtained by e-mail to:  &lt;a href="mailto:tma@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
+          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -743,17 +743,17 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E76</t>
+          <t>eth.locationLink.E76</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>On-site use only after confirmed appointment with &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Appointment for on-site use von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Benutzung vor Ort nur nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt;</t>
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -773,17 +773,17 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E79</t>
+          <t>eth.locationHint.E76</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/en/library" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
+          <t>On-site use only after confirmed appointment with &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Appointment for on-site use von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/de/bibliothek" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
+          <t>Benutzung vor Ort nur nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E79</t>
+          <t>eth.locationLink.E79</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
+          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/en/library" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
+          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/de/bibliothek" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -833,17 +833,17 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E98.E98AZ</t>
+          <t>eth.locationHint.E79</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://afz.ethz.ch/en/search-visit/search/library.html" target="_blank" &gt;Archives of Contemporary History&lt;a&gt;</t>
+          <t>&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://afz.ethz.ch/recherche-archivbesuch/recherche/bibliothek.html" target="_blank" &gt;Archiv für Zeitgeschichte&lt;a&gt;</t>
+          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>metagrid.link.open</t>
+          <t>eth.locationLink.E98.E98AZ</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Show Metagrid links</t>
+          <t>&lt;a href="https://afz.ethz.ch/en/search-visit/search/library.html" target="_blank" &gt;Archives of Contemporary History&lt;a&gt;</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Metagrid-Links zeigen</t>
+          <t>&lt;a href="https://afz.ethz.ch/recherche-archivbesuch/recherche/bibliothek.html" target="_blank" &gt;Archiv für Zeitgeschichte&lt;a&gt;</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>metagrid.link.close</t>
+          <t>metagrid.link.open</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Hide Metagrid links</t>
+          <t>Show Metagrid links</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Metagrid-Links ausblenden</t>
+          <t>Metagrid-Links zeigen</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.text1</t>
+          <t>metagrid.link.close</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Article/chapter is not held in the swisscovery Network or cannot be requested.</t>
+          <t>Hide Metagrid links</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Artikel/Kapitel ist im swisscovery Network nicht vorhanden oder nicht bestellbar.</t>
+          <t>Metagrid-Links ausblenden</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.text2</t>
+          <t>eth.illLink.text1</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Please request via</t>
+          <t>Article/chapter is not held in the swisscovery Network or cannot be requested.</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Bestellen Sie bitte via</t>
+          <t>Artikel/Kapitel ist im swisscovery Network nicht vorhanden oder nicht bestellbar.</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.text3</t>
+          <t>eth.illLink.text2</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Please request via</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Bestellen Sie bitte via</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.linkText</t>
+          <t>eth.illLink.text3</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>interlibrary loan</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Fernleihe</t>
+          <t>.</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.url</t>
+          <t>eth.illLink.linkText</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/order-forms/interlibrary-loans-ordering-copies.html</t>
+          <t>interlibrary loan</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/bestellformulare/fernleihe-kopien-bestellen.html</t>
+          <t>Fernleihe</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>46097.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="33">
@@ -1073,17 +1073,17 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>eth.composeErara.print</t>
+          <t>eth.illLink.url</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Print item in ETH swisscovery</t>
+          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/order-forms/interlibrary-loans-ordering-copies.html</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>Print-Exemplar in ETH swisscovery</t>
+          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/bestellformulare/fernleihe-kopien-bestellen.html</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>46058.0</v>
+        <v>46097.0</v>
       </c>
     </row>
     <row r="34">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>eth.composeErara.online</t>
+          <t>eth.composeErara.print</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Online item in ETH swisscovery (from e-rara)</t>
+          <t>Print item in ETH swisscovery</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Online-Exemplar in ETH swisscovery (e-rara)</t>
+          <t>Print-Exemplar in ETH swisscovery</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>eth.composeErara.emaps</t>
+          <t>eth.composeErara.online</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Georeferenced online item in ETH swisscovery (from e-maps)</t>
+          <t>Online item in ETH swisscovery (from e-rara)</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>Georeferenziertes Online-Exemplar in ETH swisscovery (e-maps)</t>
+          <t>Online-Exemplar in ETH swisscovery (e-rara)</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>eth.composeErara.geoTiff</t>
+          <t>eth.composeErara.emaps</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>GeoTIFF map via e-maps</t>
+          <t>Georeferenced online item in ETH swisscovery (from e-maps)</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>GeoTIFF via e-maps</t>
+          <t>Georeferenziertes Online-Exemplar in ETH swisscovery (e-maps)</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>eth.composeNb.print</t>
+          <t>eth.composeErara.geoTiff</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Print item in in ETH swisscovery</t>
+          <t>GeoTIFF map via e-maps</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>Print-Exemplar in ETH swisscovery</t>
+          <t>GeoTIFF via e-maps</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>eth.composeNb.online</t>
+          <t>eth.composeNb.print</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Online item in ETH swisscovery</t>
+          <t>Print item in in ETH swisscovery</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>Online-Exemplar in ETH swisscovery</t>
+          <t>Print-Exemplar in ETH swisscovery</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>eth.dnbToc.toc</t>
+          <t>eth.composeNb.online</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Table of content from the DNB for</t>
+          <t>Online item in ETH swisscovery</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>Inhaltsverzeichnis der DNB zu</t>
+          <t>Online-Exemplar in ETH swisscovery</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>eth.dnbToc.text</t>
+          <t>eth.dnbToc.toc</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Content description from the DNB for</t>
+          <t>Table of content from the DNB for</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>Inhaltstext der DNB zu</t>
+          <t>Inhaltsverzeichnis der DNB zu</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>eth.libraryStack.text1</t>
+          <t>eth.dnbToc.text</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Password protected access. Restricted to members of ETH Zurich only.</t>
+          <t>Content description from the DNB for</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>Passwortgeschützter Zugang. Nur für Mitglieder der ETH Zürich zugänglich.</t>
+          <t>Inhaltstext der DNB zu</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>eth.libraryStack.text2</t>
+          <t>eth.libraryStack.text1</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>You need to register with your ETH Zurich e-mail address "Sign In". Access to this source is restricted on the domain ethz.ch because of license restrictions.</t>
+          <t>Password protected access. Restricted to members of ETH Zurich only.</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Sie müssen sich mit Ihrer ETH Zürich E-Mail-Adresse unter „Anmelden” registrieren. Der Zugriff auf diese Quelle ist aufgrund von Lizenzbeschränkungen auf die Domain ethz.ch eingeschränkt.</t>
+          <t>Passwortgeschützter Zugang. Nur für Mitglieder der ETH Zürich zugänglich.</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>eth.wayback.text</t>
+          <t>eth.libraryStack.text2</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>In the web archive, select a year and a date marked in blue to access the archived website.</t>
+          <t>You need to register with your ETH Zurich e-mail address "Sign In". Access to this source is restricted on the domain ethz.ch because of license restrictions.</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>Wählen Sie im Webarchiv ein Jahr und ein blau markiertes Datum, um die archivierte Website aufzurufen.</t>
+          <t>Sie müssen sich mit Ihrer ETH Zürich E-Mail-Adresse unter „Anmelden” registrieren. Der Zugriff auf diese Quelle ist aufgrund von Lizenzbeschränkungen auf die Domain ethz.ch eingeschränkt.</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>eth.wayback.linkText</t>
+          <t>eth.wayback.text</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Link to the web archive</t>
+          <t>In the web archive, select a year and a date marked in blue to access the archived website.</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>Link zum Webarchiv</t>
+          <t>Wählen Sie im Webarchiv ein Jahr und ein blau markiertes Datum, um die archivierte Website aufzurufen.</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1433,17 +1433,17 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>eth.onlineProblem.linkText</t>
+          <t>eth.wayback.linkText</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Report access problem</t>
+          <t>Link to the web archive</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>Zugriffsproblem melden</t>
+          <t>Link zum Webarchiv</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>eth.onlineProblem.ariaLabel</t>
+          <t>eth.onlineProblem.linkText</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Report access problem by email</t>
+          <t>Report access problem</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>Zugriffsproblem per E-Mail melden</t>
+          <t>Zugriffsproblem melden</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -1493,17 +1493,17 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>eth.registrationLink.linkText</t>
+          <t>eth.onlineProblem.ariaLabel</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Not registered yet?</t>
+          <t>Report access problem by email</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>Noch nicht registriert?</t>
+          <t>Zugriffsproblem per E-Mail melden</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -1523,17 +1523,17 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>eth.onlineButton.linkText</t>
+          <t>eth.registrationLink.linkText</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>View Online</t>
+          <t>Not registered yet?</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>Online ansehen</t>
+          <t>Noch nicht registriert?</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>eth.okm.label</t>
+          <t>eth.onlineButton.linkText</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Search for “{{ search }}” in Open Knowledge Maps:</t>
+          <t>View Online</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>Suche nach “{{ search }}” in Open Knowledge Maps:</t>
+          <t>Online ansehen</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>eth.logoSubline.subline</t>
+          <t>eth.okm.label</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>ETH swisscovery</t>
+          <t>Search for “{{ search }}” in Open Knowledge Maps:</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>ETH swisscovery</t>
+          <t>Suche nach “{{ search }}” in Open Knowledge Maps:</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.text1</t>
+          <t>eth.logoSubline.subline</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Link your SWICTH edu-ID to your ETH Zurich user account in</t>
+          <t>ETH swisscovery</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfen Sie Ihre SWITCH edu-ID mit Ihrem ETH-Benutzerkonto in</t>
+          <t>ETH swisscovery</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.text2</t>
+          <t>eth.idpWarning.text1</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>to benefit from the advantages for members of ETH Zurich.</t>
+          <t>Link your SWICTH edu-ID to your ETH Zurich user account in</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>, um von den Vorteilen für ETH-Angehörige zu profitieren.</t>
+          <t>Verknüpfen Sie Ihre SWITCH edu-ID mit Ihrem ETH-Benutzerkonto in</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.linkText2</t>
+          <t>eth.idpWarning.text2</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>Instructions</t>
+          <t>to benefit from the advantages for members of ETH Zurich.</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>Anleitung</t>
+          <t>, um von den Vorteilen für ETH-Angehörige zu profitieren.</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.linkText1</t>
+          <t>eth.idpWarning.linkText2</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>www.password.ethz.ch</t>
+          <t>Instructions</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>www.password.ethz.ch</t>
+          <t>Anleitung</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -1733,17 +1733,17 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.link1</t>
+          <t>eth.idpWarning.linkText1</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>https://www.password.ethz.ch/authentication/login_en.html</t>
+          <t>www.password.ethz.ch</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>https://www.password.ethz.ch/</t>
+          <t>www.password.ethz.ch</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.link2</t>
+          <t>eth.idpWarning.link1</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/frequently-asked-questions.html#eth-card-as-user-id</t>
+          <t>https://www.password.ethz.ch/authentication/login_en.html</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/faq.html#eth-karte-als-benutzungsausweis</t>
+          <t>https://www.password.ethz.ch/</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>46163.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="57">
@@ -1793,17 +1793,17 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.heading</t>
+          <t>eth.idpWarning.link2</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Address changes</t>
+          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/frequently-asked-questions.html#eth-card-as-user-id</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>Adresse bearbeiten</t>
+          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/faq.html#eth-karte-als-benutzungsausweis</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>46058.0</v>
+        <v>46163.0</v>
       </c>
     </row>
     <row r="58">
@@ -1823,17 +1823,17 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembers</t>
+          <t>eth.changeAddress.heading</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Members of ETH</t>
+          <t>Address changes</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>ETH-Angehörige</t>
+          <t>Adresse bearbeiten</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersIntro</t>
+          <t>eth.changeAddress.ethMembers</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Change your address in 2 steps:</t>
+          <t>Members of ETH</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>Ändern Sie Ihre Adresse in 2 Schritten:</t>
+          <t>ETH-Angehörige</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -1883,17 +1883,17 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersStep1</t>
+          <t>eth.changeAddress.ethMembersIntro</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>1. Change address:</t>
+          <t>Change your address in 2 steps:</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>1. Adresse ändern:</t>
+          <t>Ändern Sie Ihre Adresse in 2 Schritten:</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersStep2</t>
+          <t>eth.changeAddress.ethMembersStep1</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>2. Confirm address change:</t>
+          <t>1. Change address:</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>2. Adressänderung bestätigen:</t>
+          <t>1. Adresse ändern:</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -1943,17 +1943,17 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.otherCustomers</t>
+          <t>eth.changeAddress.ethMembersStep2</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Private individuals</t>
+          <t>2. Confirm address change:</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>Privatpersonen</t>
+          <t>2. Adressänderung bestätigen:</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.otherCustomersIntro</t>
+          <t>eth.changeAddress.otherCustomers</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Change your address here:</t>
+          <t>Private individuals</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>Ändern Sie Ihre Adresse hier:</t>
+          <t>Privatpersonen</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersStep1Url</t>
+          <t>eth.changeAddress.otherCustomersIntro</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>https://idapps.ethz.ch/contact-data/</t>
+          <t>Change your address here:</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>https://idapps.ethz.ch/contact-data/</t>
+          <t>Ändern Sie Ihre Adresse hier:</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>46141.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="65">
@@ -2033,17 +2033,17 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersStep2Url</t>
+          <t>eth.changeAddress.ethMembersStep1Url</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>https://eduid.ch</t>
+          <t>https://idapps.ethz.ch/contact-data/</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>https://eduid.ch</t>
+          <t>https://idapps.ethz.ch/contact-data/</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>46058.0</v>
+        <v>46141.0</v>
       </c>
     </row>
     <row r="66">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.otherCustomersUrl</t>
+          <t>eth.changeAddress.ethMembersStep2Url</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>eth.bibNews.all</t>
+          <t>eth.changeAddress.otherCustomersUrl</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>All news</t>
+          <t>https://eduid.ch</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>Alle News</t>
+          <t>https://eduid.ch</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -2123,17 +2123,17 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>eth.geoRef.heading</t>
+          <t>eth.bibNews.all</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Related Places</t>
+          <t>All news</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfte Orte</t>
+          <t>Alle News</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>eth.geoRef.entity</t>
+          <t>eth.geoRef.heading</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Related Places</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>Ort</t>
+          <t>Verknüpfte Orte</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -2183,17 +2183,17 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>eth.provenance.heading</t>
+          <t>eth.geoRef.entity</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Provenance marks</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>Provenienzen</t>
+          <t>Ort</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>eth.provenance.entity</t>
+          <t>eth.provenance.heading</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Provenance marks</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>Provenienz</t>
+          <t>Provenienzen</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>eth.provenance.date</t>
+          <t>eth.provenance.entity</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Date:</t>
+          <t>Provenance</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>Datierung:</t>
+          <t>Provenienz</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>eth.provenance.epicsLinkText</t>
+          <t>eth.provenance.date</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Provenance in E-Pics</t>
+          <t>Date:</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>Provenienz in E-Pics</t>
+          <t>Datierung:</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.entity</t>
+          <t>eth.provenance.epicsLinkText</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Provenance in E-Pics</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Provenienz in E-Pics</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.photo</t>
+          <t>eth.personCard.entity</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Photo of</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>Photo von</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.licence</t>
+          <t>eth.personCard.photo</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Licence for the picture see</t>
+          <t>Photo of</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>Lizenz für das Bild siehe</t>
+          <t>Photo von</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.heading</t>
+          <t>eth.personCard.licence</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Related Persons</t>
+          <t>Licence for the picture see</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfte Personen</t>
+          <t>Lizenz für das Bild siehe</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
@@ -2423,17 +2423,17 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.headingMore</t>
+          <t>eth.personCard.heading</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>More related Persons</t>
+          <t>Related Persons</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>Mehr Personen</t>
+          <t>Verknüpfte Personen</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -2453,17 +2453,17 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.topics</t>
+          <t>eth.personCard.headingMore</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Topics in ETH swisscovery</t>
+          <t>More related Persons</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>Geografisches Schlagwort in ETH swisscovery</t>
+          <t>Mehr Personen</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -2483,17 +2483,17 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.ethorama</t>
+          <t>eth.placePage.topics</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Documents in ETHorama</t>
+          <t>Topics in ETH swisscovery</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>Dokumente in ETHorama</t>
+          <t>Geografisches Schlagwort in ETH swisscovery</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -2513,17 +2513,17 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.ethoramaTopics</t>
+          <t>eth.placePage.ethorama</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>ETHorama thematic collections</t>
+          <t>Documents in ETHorama</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>ETHorama Themensammlungen</t>
+          <t>Dokumente in ETHorama</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.ethoramaRoutes</t>
+          <t>eth.placePage.ethoramaTopics</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>ETHorama historical travels</t>
+          <t>ETHorama thematic collections</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>ETHorama Historische Reisen</t>
+          <t>ETHorama Themensammlungen</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -2573,17 +2573,17 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.wikidata</t>
+          <t>eth.placePage.ethoramaRoutes</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Links from Wikidata</t>
+          <t>ETHorama historical travels</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>Links from Wikidata</t>
+          <t>ETHorama Historische Reisen</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -2603,17 +2603,17 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.maps</t>
+          <t>eth.placePage.wikidata</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Historical maps</t>
+          <t>Links from Wikidata</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>Historische Karten</t>
+          <t>Links from Wikidata</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.mapsList</t>
+          <t>eth.placePage.maps</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Historical maps as list</t>
+          <t>Historical maps</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>Historische Karten als Liste</t>
+          <t>Historische Karten</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.searchVariants</t>
+          <t>eth.placePage.mapsList</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Search variants in all data of the ETH Library</t>
+          <t>Historical maps as list</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>Suchvarianten in allen Daten der ETH-Bibliothek</t>
+          <t>Historische Karten als Liste</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.results</t>
+          <t>eth.personPage.searchVariants</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>results</t>
+          <t>Search variants in all data of the ETH Library</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>Ergebnisse</t>
+          <t>Suchvarianten in allen Daten der ETH-Bibliothek</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.authorityLinking</t>
+          <t>eth.personPage.results</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>Authority data</t>
+          <t>results</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>Normdaten</t>
+          <t>Ergebnisse</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -2753,17 +2753,17 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.researcherProfile</t>
+          <t>eth.personPage.authorityLinking</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>Researcher profiles</t>
+          <t>Authority data</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>Forscherprofile</t>
+          <t>Normdaten</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -2783,17 +2783,17 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.archives</t>
+          <t>eth.personPage.researcherProfile</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>Archives</t>
+          <t>Researcher profiles</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Forscherprofile</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -2813,17 +2813,17 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.metagrid</t>
+          <t>eth.personPage.archives</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>Metagrid</t>
+          <t>Archives</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>Metagrid</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.wikidata</t>
+          <t>eth.personPage.metagrid</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Wikidata</t>
+          <t>Metagrid</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>Wikidata</t>
+          <t>Metagrid</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheus</t>
+          <t>eth.personPage.wikidata</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>Wikidata</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>Wikidata</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
@@ -2903,17 +2903,17 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.students</t>
+          <t>eth.personPage.prometheus</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>Students (Wikidata)</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>Studenten (Wikidata)</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.teacher</t>
+          <t>eth.personPage.students</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>Teachers (Wikidata)</t>
+          <t>Students (Wikidata)</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>Lehrer (Wikidata)</t>
+          <t>Studenten (Wikidata)</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.relatedGnd</t>
+          <t>eth.personPage.teacher</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>Related persons from GND</t>
+          <t>Teachers (Wikidata)</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>Verbundene Personen nach GND</t>
+          <t>Lehrer (Wikidata)</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
@@ -2993,17 +2993,17 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheusIntro1</t>
+          <t>eth.personPage.relatedGnd</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>Links from the</t>
+          <t>Related persons from GND</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>Links vom</t>
+          <t>Verbundene Personen nach GND</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
@@ -3023,17 +3023,17 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheusIntro2</t>
+          <t>eth.personPage.prometheusIntro1</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Aggregator of the</t>
+          <t>Links from the</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Aggregator des</t>
+          <t>Links vom</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheusIntro3</t>
+          <t>eth.personPage.prometheusIntro2</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>LMU Center for Digital Humanities</t>
+          <t>Aggregator of the</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>LMU Center for Digital Humanities</t>
+          <t>Aggregator des</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
@@ -3083,17 +3083,17 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.searchName</t>
+          <t>eth.personPage.prometheusIntro3</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>Search by name</t>
+          <t>LMU Center for Digital Humanities</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>Suche nach Namen</t>
+          <t>LMU Center for Digital Humanities</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.searchGnd</t>
+          <t>eth.personPage.searchName</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>Search by GND ID</t>
+          <t>Search by name</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>Suche nach GND ID</t>
+          <t>Suche nach Namen</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.searchGndBirth</t>
+          <t>eth.personPage.searchGnd</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Search by name and (GND ID or birthyear)</t>
+          <t>Search by GND ID</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>Suche nach Name und (GND ID oder Geburtsjahr)</t>
+          <t>Suche nach GND ID</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.born</t>
+          <t>eth.personPage.searchGndBirth</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Born:</t>
+          <t>Search by name and (GND ID or birthyear)</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>Geboren:</t>
+          <t>Suche nach Name und (GND ID oder Geburtsjahr)</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
@@ -3203,17 +3203,17 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheusAll</t>
+          <t>eth.personPage.born</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>All links from Prometheus</t>
+          <t>Born:</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>Alle Links von Prometheus</t>
+          <t>Geboren:</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>eth.provenienzEraraLink.erara</t>
+          <t>eth.personPage.prometheusAll</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Source in e-rara</t>
+          <t>All links from Prometheus</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>Quelle in e-rara</t>
+          <t>Alle Links von Prometheus</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
@@ -3263,17 +3263,17 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>eth.provenienzEraraLink.swisscovery</t>
+          <t>eth.provenienzEraraLink.erara</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>Details provenance mark</t>
+          <t>Source in e-rara</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>Details Provenienzvermerk</t>
+          <t>Quelle in e-rara</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -3293,17 +3293,17 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>eth.bibNews.heading</t>
+          <t>eth.provenienzEraraLink.swisscovery</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Details provenance mark</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Details Provenienzvermerk</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>eth.gitHint.heading</t>
+          <t>eth.bibNews.heading</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>important information</t>
+          <t>News</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>Wichtiger Hinweis</t>
+          <t>News</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -3353,17 +3353,17 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.website</t>
+          <t>eth.gitHint.heading</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>important information</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>Webseite</t>
+          <t>Wichtiger Hinweis</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>eth.rapidoEthmemberHint.text</t>
+          <t>eth.locationLink.website</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>Please check in the upper ordering section if one of the libraries at ETH Zurich offers "Digitization" (free service).</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>Überprüfen Sie bitte im oberen Bestellbereich, ob eine Bibliothek der ETH Zürich "Digitalisierung" anbietet (kostenloser Service).</t>
+          <t>Webseite</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46108.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="111">
@@ -3413,17 +3413,17 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>41SLSP_ETH:TMI_NDE.eth.composeNb.print</t>
+          <t>eth.rapidoEthmemberHint.text</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>Print item in TMI Research</t>
+          <t>Please check in the upper ordering section if one of the libraries at ETH Zurich offers "Digitization" (free service).</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>Print-Exemplar in TMI Research</t>
+          <t>Überprüfen Sie bitte im oberen Bestellbereich, ob eine Bibliothek der ETH Zürich "Digitalisierung" anbietet (kostenloser Service).</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>46113.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="112">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>41SLSP_ETH:TMI_NDE.eth.composeNb.online</t>
+          <t>41SLSP_ETH:TMI_NDE.eth.composeNb.print</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>Online item in TMI Research</t>
+          <t>Print item in TMI Research</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>Online-Exemplar in TMI Research</t>
+          <t>Print-Exemplar in TMI Research</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -3473,17 +3473,17 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>41SLSP_ETH:TMI_NDE.eth.logoSubline.subline</t>
+          <t>41SLSP_ETH:TMI_NDE.eth.composeNb.online</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>TMI Research</t>
+          <t>Online item in TMI Research</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>TMI Research</t>
+          <t>Online-Exemplar in TMI Research</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
@@ -3503,17 +3503,17 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>eth.requestHint.request</t>
+          <t>41SLSP_ETH:TMI_NDE.eth.logoSubline.subline</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00 (free of charge to ETH institutional address)</t>
+          <t>TMI Research</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00 (kostenlos an ETH-Institutsadresse)</t>
+          <t>TMI Research</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>46141.0</v>
+        <v>46113.0</v>
       </c>
     </row>
     <row r="115">
@@ -3533,17 +3533,17 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>eth.requestHint.digitization</t>
+          <t>eth.requestHint.request</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>Normal fee: CHF 5.00&lt;br&gt;ETH employees: free of charge&lt;br&gt;All students: CHF 2.50&lt;br&gt;Commercial clients: CHF 25.00</t>
+          <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00 (free of charge to ETH institutional address)</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>Normale Gebühr: CHF 5.00&lt;br&gt;ETH-Mitarbeitende: kostenlos&lt;br&gt;Alle Studierende: CHF 2.50&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
+          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00 (kostenlos an ETH-Institutsadresse)</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
@@ -3563,17 +3563,17 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>tmi.getit.E73BI</t>
+          <t>eth.requestHint.digitization</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>&lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;Can be used in the reading room of the Thomas Mann Archives subject to prior appointment.&lt;/div&gt; &lt;div&gt;Contact: &lt;a href="mailto:tma@library.ethz.ch?subject=Appointment for: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH&amp;docid=alma{{id}}"&gt;         &lt;span&gt;More Informations in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
+          <t>Normal fee: CHF 5.00&lt;br&gt;ETH employees: free of charge&lt;br&gt;All students: CHF 2.50&lt;br&gt;Commercial clients: CHF 25.00</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;Benutzung im Lesesaal des Thomas-Mann-Archivs auf Voranmeldung.&lt;/div&gt; &lt;div&gt;Kontakt: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH&amp;docid=alma{{id}}"&gt;         &lt;span&gt;Mehr Informationen in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
+          <t>Normale Gebühr: CHF 5.00&lt;br&gt;ETH-Mitarbeitende: kostenlos&lt;br&gt;Alle Studierende: CHF 2.50&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>46149.0</v>
+        <v>46141.0</v>
       </c>
     </row>
     <row r="117">
@@ -3593,17 +3593,17 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>eth.requestHint.digitizationOtherLibrary</t>
+          <t>tmi.getit.E73BI</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>Normal fee: CHF 5.00&lt;br&gt;Commercial clients: CHF 25.00</t>
+          <t>&lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;Can be used in the reading room of the Thomas Mann Archives subject to prior appointment.&lt;/div&gt; &lt;div&gt;Contact: &lt;a href="mailto:tma@library.ethz.ch?subject=Appointment for: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH_NDE&amp;docid=alma{{id}}"&gt;         &lt;span&gt;More Informations in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>Normale Gebühr: CHF 5.00&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
+          <t>&lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;Benutzung im Lesesaal des Thomas-Mann-Archivs auf Voranmeldung.&lt;/div&gt; &lt;div&gt;Kontakt: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH_NDE&amp;docid=alma{{id}}"&gt;         &lt;span&gt;Mehr Informationen in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>46142.0</v>
+        <v>46184.0</v>
       </c>
     </row>
     <row r="118">
@@ -3623,17 +3623,17 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>tmi.getit.tmhla</t>
+          <t>eth.requestHint.digitizationOtherLibrary</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>&lt;div&gt;       &lt;span&gt;Not loanable.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Can be used in the library of the Thomas Mann House by prior appointment. Please contact&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Request about: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
+          <t>Normal fee: CHF 5.00&lt;br&gt;Commercial clients: CHF 25.00</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>&lt;div&gt;  &lt;span&gt;Nicht ausleihbar.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Benutzung nach vorheriger Anmeldung in der Bibliothek des Thomas-Mann-Hauses. Bitte kontaktieren Sie&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Anfrage zu: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
+          <t>Normale Gebühr: CHF 5.00&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
     </row>
     <row r="119">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>eth.requestHint.requestOtherLibrary</t>
+          <t>tmi.getit.tmhla</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00</t>
+          <t>&lt;div&gt;       &lt;span&gt;Not loanable.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Can be used in the library of the Thomas Mann House by prior appointment. Please contact&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Request about: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00</t>
+          <t>&lt;div&gt;  &lt;span&gt;Nicht ausleihbar.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Benutzung nach vorheriger Anmeldung in der Bibliothek des Thomas-Mann-Hauses. Bitte kontaktieren Sie&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Anfrage zu: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>46142.0</v>
+        <v>46149.0</v>
       </c>
     </row>
     <row r="120">
@@ -3683,17 +3683,17 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>tmi.getit.luebeck</t>
+          <t>eth.requestHint.requestOtherLibrary</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailed information in the online database of the Buddenbrookhaus     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Not possible to order.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digital copies can be requested from Buddenbrookhaus (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Request about: {{callNumber}}"&gt;Contact&lt;/a&gt; ).     &lt;/div&gt;</t>
+          <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailinformationen in der Online-Datenbank des Buddenbrookhauses     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Keine Bestellung möglich.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digitalisate können beim Buddenbrookhaus angefragt werden (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Anfrage zu: {{callNumber}}"&gt;Kontakt&lt;/a&gt; ).     &lt;/div&gt;</t>
+          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
     </row>
     <row r="121">
@@ -3713,17 +3713,17 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>tmi.viewit.monacensia</t>
+          <t>tmi.getit.luebeck</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;Detailed information in the Kalliope Union Catalog (metadata only) &lt;/a&gt; &lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;     Archival materials can be viewed on site at the Monacensia im Hildebrandhaus (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Request digitized copy with signature: {{callNumber}}"&gt;       Contact     &lt;/a&gt; ). &lt;/div&gt;</t>
+          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailed information in the online database of the Buddenbrookhaus     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Not possible to order.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digital copies can be requested from Buddenbrookhaus (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Request about: {{callNumber}}"&gt;Contact&lt;/a&gt; ).     &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;     Detailinformationen in der Online-Datenbank der Monacensia im Hildebrandhaus (nur Metadaten) &lt;/a&gt; &lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;     Archivalien können vor Ort in der Monacensia im Hildebrandhaus eingesehen werden (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Anfrage Digitalisat mit Signatur "{{callNumber}}""&gt;       Kontakt     &lt;/a&gt; ). &lt;/div&gt;</t>
+          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailinformationen in der Online-Datenbank des Buddenbrookhauses     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Keine Bestellung möglich.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digitalisate können beim Buddenbrookhaus angefragt werden (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Anfrage zu: {{callNumber}}"&gt;Kontakt&lt;/a&gt; ).     &lt;/div&gt;</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>46155.0</v>
+        <v>46149.0</v>
       </c>
     </row>
     <row r="122">
@@ -3743,17 +3743,17 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>tmi.viewit.monacensia.heading</t>
+          <t>tmi.viewit.monacensia</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;Detailed information in the Kalliope Union Catalog (metadata only) &lt;/a&gt; &lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;     Archival materials can be viewed on site at the Monacensia im Hildebrandhaus (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Request digitized copy with signature: {{callNumber}}"&gt;       Contact     &lt;/a&gt; ). &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>Zugang</t>
+          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;     Detailinformationen in der Online-Datenbank der Monacensia im Hildebrandhaus (nur Metadaten) &lt;/a&gt; &lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;     Archivalien können vor Ort in der Monacensia im Hildebrandhaus eingesehen werden (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Anfrage Digitalisat mit Signatur "{{callNumber}}""&gt;       Kontakt     &lt;/a&gt; ). &lt;/div&gt;</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
@@ -3773,17 +3773,17 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>41SLSP_ETH:TMI_NDE.nde.landing.header</t>
+          <t>tmi.viewit.monacensia.heading</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>NOT_DEFINED</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>NOT_DEFINED</t>
+          <t>Zugang</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>46164.0</v>
+        <v>46155.0</v>
       </c>
     </row>
     <row r="124">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>eth.onlineProblem.mail</t>
+          <t>41SLSP_ETH:TMI_NDE.nde.landing.header</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>almakb@library.ethz.ch</t>
+          <t>NOT_DEFINED</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>almakb@library.ethz.ch</t>
+          <t>NOT_DEFINED</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>46169.0</v>
+        <v>46164.0</v>
       </c>
     </row>
     <row r="125">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>eth.topbarMessage.message</t>
+          <t>eth.onlineProblem.mail</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>NOT_DEFINED</t>
+          <t>almakb@library.ethz.ch</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>NOT_DEFINED</t>
+          <t>almakb@library.ethz.ch</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>46178.0</v>
+        <v>46169.0</v>
       </c>
     </row>
     <row r="126">
@@ -3863,17 +3863,17 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>eth.topbarMessage.heading</t>
+          <t>eth.topbarMessage.message</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Important information</t>
+          <t>EN:✨Bücherbestellungen unter 'Weitere Bestelloptionen' momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>Wichtiger Hinweis</t>
+          <t>DE:✨Bücherbestellungen unter 'Weitere Bestelloptionen' momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>46176.0</v>
+        <v>46183.0</v>
       </c>
     </row>
     <row r="127">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>eth.topbarMessage.message.41SLSP_ETH:ETH_CUSTOMIZING</t>
+          <t>eth.topbarMessage.heading</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>ETH:✨Bücherbestellungen unter 'Weitere Bestelloptionen' momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
+          <t>Important information</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>Testen Sie die Beta-Version des neuen KI-gestützten Research Assistant!  &lt;a href=\"https://library.ethz.ch/en/searching-and-using/research-assistant.html\" target=\"_blank\"&gt;Learn more&lt;/a&gt;</t>
+          <t>Wichtiger Hinweis</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>46177.0</v>
+        <v>46176.0</v>
       </c>
     </row>
     <row r="128">
@@ -3923,17 +3923,17 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>tmi.topbarMessage.message</t>
+          <t>eth.topbarMessage.message.41SLSP_ETH:ETH_CUSTOMIZING</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>TMI EN:✨das und das momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
+          <t>ETH View:✨Bücherbestellungen unter 'Weitere Bestelloptionen' momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>TMI DE:✨das und das  nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
+          <t>Testen Sie die Beta-Version des neuen KI-gestützten Research Assistant!  &lt;a href=\"https://library.ethz.ch/en/searching-and-using/research-assistant.html\" target=\"_blank\"&gt;Learn more&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>46178.0</v>
+        <v>46177.0</v>
       </c>
     </row>
     <row r="129">
@@ -3953,17 +3953,17 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>tmi.topbarMessage.heading</t>
+          <t>tmi.topbarMessage.message</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>Important information</t>
+          <t>TMI EN:✨das und das momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>Wichtiger Hinweis</t>
+          <t>TMI DE:✨das und das  nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -3975,8 +3975,98 @@
         <v>46178.0</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>tmi.topbarMessage.heading</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>Important information</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>Wichtiger Hinweis</t>
+        </is>
+      </c>
+      <c r="E130" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>46178.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>tmi.composeErara.print</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>Print item in in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>Print-Exemplar in TMI Research</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>46190.0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>tmi.composeErara.online</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>Online item in in ETH swisscovery</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>Online-Exemplar in TMI Research</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>46190.0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F129"/>
+  <autoFilter ref="A1:F132"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/misc/customizing-labels.xlsx
+++ b/misc/customizing-labels.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$111</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -96,7 +96,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="8.59375" customWidth="true"/>
-    <col min="2" max="2" width="59.34765625" customWidth="true"/>
+    <col min="2" max="2" width="50.80859375" customWidth="true"/>
     <col min="3" max="3" width="255.0" customWidth="true"/>
     <col min="4" max="4" width="27.34375" customWidth="true"/>
     <col min="5" max="5" width="27.34375" customWidth="true"/>
@@ -173,26 +173,26 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E06.E06LI</t>
+          <t>slsp.topbarMessage.message</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>The library Chair for Literature and Cultural Studies is &lt;strong&gt;not&lt;/strong&gt; located at GESS Library.&lt;br&gt;&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; possible.</t>
+          <t>NOT_DEFINED</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Die Bibliothek Professur für Literatur- und Kulturwissenschaft befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; möglich.</t>
+          <t>NOT_DEFINED</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46058.0</v>
+        <v>46210.0</v>
       </c>
     </row>
     <row r="4">
@@ -203,26 +203,26 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E01.AETH</t>
+          <t>slsp.onlineButton.linkText</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;On-site use&lt;/strong&gt; only after appointment with &lt;a href="mailto:archiv@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
+          <t>View Online</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach Voranmeldung bei &lt;a href="mailto:archiv@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
+          <t>Online ansehen</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46058.0</v>
+        <v>46210.0</v>
       </c>
     </row>
     <row r="5">
@@ -233,26 +233,26 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.default</t>
+          <t>slsp.topbarMessage.heading</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
+          <t>Important Message</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
+          <t>Wichtiger Hinweis</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46058.0</v>
+        <v>46210.0</v>
       </c>
     </row>
     <row r="6">
@@ -263,26 +263,26 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E01</t>
+          <t>slsp.changeAvailability.otherInstitution.print</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
+          <t>Not available at this library&lt;br&gt;Copies are available only at other swisscovery libraries</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
+          <t>Nicht an dieser Bibliothek verfügbar&lt;br&gt;Verfügbarkeit von Prints nur an anderen swisscovery Bibliotheken</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46058.0</v>
+        <v>46210.0</v>
       </c>
     </row>
     <row r="7">
@@ -293,26 +293,26 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E03</t>
+          <t>slsp.changeAvailability.otherInstitution.online</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
+          <t>Not available at this library&lt;br&gt;Online access only at other swisscovery libraries</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
+          <t>Nicht an dieser Bibliothek verfügbar&lt;br&gt;Online-Zugriff nur an anderen swisscovery-Bibliotheken</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46058.0</v>
+        <v>46210.0</v>
       </c>
     </row>
     <row r="8">
@@ -323,26 +323,26 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E06.E06LI</t>
+          <t>slsp.changeAvailability.otherInstitution.printAndOnline</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
+          <t>Not available at this library&lt;br&gt;Online access and Copies only at other swisscovery libraries</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
+          <t>Nicht an dieser Bibliothek verfügbar&lt;br&gt;Verfügbarkeit von Prints und Online Ressourcen nur an anderen swisscovery Bibliotheken</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46058.0</v>
+        <v>46210.0</v>
       </c>
     </row>
     <row r="9">
@@ -353,17 +353,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>eth.offcampusWarning.text1</t>
+          <t>eth.illLink.text1</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>ETH Library’s licensed e-resources are accessible via the ETH network or</t>
+          <t>Article/chapter is not held in the swisscovery Network or cannot be requested from a library at ETH Zurich.</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Lizenzierte E-Ressourcen der ETH-Bibliothek sind über das ETH-Netzwerk oder</t>
+          <t xml:space="preserve">Artikel/Kapitel ist im swisscovery Netzwerk nicht vorhanden oder  nicht an eine Bibliothek der ETH Zürich bestellbar. </t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -372,7 +372,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46058.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="10">
@@ -383,17 +383,17 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>eth.offcampusWarning.text2</t>
+          <t>eth.illLink.text2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Please request via</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>zugänglich.</t>
+          <t>Bestellen Sie bitte via</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -413,17 +413,17 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>eth.offcampusWarning.url</t>
+          <t>eth.illLink.text3</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>https://unlimited.ethz.ch/en/help/network/vpn</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>https://unlimited.ethz.ch/help/network/vpn</t>
+          <t>.</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -443,17 +443,17 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>eth.offcampusWarning.linktext</t>
+          <t>eth.illLink.linkText</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>interlibrary loan</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Fernleihe</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E06.E06EQ</t>
+          <t>eth.illLink.url</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://ethz.ch/staffnet/en/employment-and-work/working-environment/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
+          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/order-forms/interlibrary-loans-ordering-copies.html</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://ethz.ch/staffnet/de/anstellung-und-arbeit/arbeitsumfeld/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
+          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/bestellformulare/fernleihe-kopien-bestellen.html</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46058.0</v>
+        <v>46097.0</v>
       </c>
     </row>
     <row r="14">
@@ -503,17 +503,17 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E06.E06EQ</t>
+          <t>eth.composeErara.print</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>The library of ETH Diversity is &lt;strong&gt;not&lt;/strong&gt; located at GESS Library.&lt;br&gt;&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:diversity@ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; possible.</t>
+          <t>Print item in ETH swisscovery</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Die Bibliothek von ETH Diversity befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:diversity@ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; möglich.</t>
+          <t>Print-Exemplar in ETH swisscovery</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>46111.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="15">
@@ -533,17 +533,17 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E33</t>
+          <t>eth.composeErara.online</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Would you like to order a scan of an article or a chapter from this document? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan Request: MMS ID {{id}}"&gt;Write to us!&lt;/a&gt;</t>
+          <t>Online item in ETH swisscovery (from e-rara)</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Möchten Sie einen Scan eines Artikels oder Kapitels aus diesem Dokument bestellen? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan-Anfrage: MMS ID {{id}}"&gt;Schreiben Sie uns!&lt;/a&gt;</t>
+          <t>Online-Exemplar in ETH swisscovery (e-rara)</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E33</t>
+          <t>eth.composeErara.emaps</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://infozentrum.ethz.ch/en/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
+          <t>Georeferenced online item in ETH swisscovery (from e-maps)</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://infozentrum.ethz.ch/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
+          <t>Georeferenziertes Online-Exemplar in ETH swisscovery (e-maps)</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E01.AETH</t>
+          <t>eth.composeErara.geoTiff</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/en/archiving-and-digitising/archiving/eth-zurich-university-archives.html" target="_blank" &gt;ETH Zurich University Archives&lt;a&gt;</t>
+          <t>GeoTIFF map via e-maps</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/archivieren-und-digitalisieren/archivieren/hochschularchiv-der-eth-zuerich.html" target="_blank" &gt;Hochschularchiv der ETH Zürich&lt;a&gt;</t>
+          <t>GeoTIFF via e-maps</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E73.E73MF</t>
+          <t>eth.composeNb.print</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
+          <t>Print item in in ETH swisscovery</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
+          <t>Print-Exemplar in ETH swisscovery</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -653,17 +653,17 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E73.E73BI</t>
+          <t>eth.composeNb.online</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
+          <t>Online item in ETH swisscovery</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
+          <t>Online-Exemplar in ETH swisscovery</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E73.E73MF</t>
+          <t>eth.dnbToc.toc</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>Use only on site. Information can be obtained by e-mail to:  &lt;a href="mailto:mfa@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt;</t>
+          <t>Table of content from the DNB for</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:mfa@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt;</t>
+          <t>Inhaltsverzeichnis der DNB zu</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E73.E73BI</t>
+          <t>eth.dnbToc.text</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Use only on site. Information can be obtained by e-mail to:  &lt;a href="mailto:tma@library.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt;</t>
+          <t>Content description from the DNB for</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt;</t>
+          <t>Inhaltstext der DNB zu</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -743,17 +743,17 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E76</t>
+          <t>eth.libraryStack.text1</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/en/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
+          <t>Password protected access. Restricted to members of ETH Zurich only.</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
+          <t>Passwortgeschützter Zugang. Nur für Mitglieder der ETH Zürich zugänglich.</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -773,17 +773,17 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E76</t>
+          <t>eth.libraryStack.text2</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>On-site use only after confirmed appointment with &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Appointment for on-site use von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt;</t>
+          <t>You need to register with your ETH Zurich e-mail address "Sign In". Access to this source is restricted on the domain ethz.ch because of license restrictions.</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Benutzung vor Ort nur nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt;</t>
+          <t>Sie müssen sich mit Ihrer ETH Zürich E-Mail-Adresse unter „Anmelden” registrieren. Der Zugriff auf diese Quelle ist aufgrund von Lizenzbeschränkungen auf die Domain ethz.ch eingeschränkt.</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E79</t>
+          <t>eth.wayback.text</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/en/library" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
+          <t>In the web archive, select a year and a date marked in blue to access the archived website.</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/de/bibliothek" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
+          <t>Wählen Sie im Webarchiv ein Jahr und ein blau markiertes Datum, um die archivierte Website aufzurufen.</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -833,17 +833,17 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>eth.locationHint.E79</t>
+          <t>eth.wayback.linkText</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;On-site use&lt;/strong&gt; only after confirmed appointment with &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Appointment for on-site use of MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
+          <t>Link to the web archive</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
+          <t>Link zum Webarchiv</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.E98.E98AZ</t>
+          <t>eth.onlineProblem.linkText</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://afz.ethz.ch/en/search-visit/search/library.html" target="_blank" &gt;Archives of Contemporary History&lt;a&gt;</t>
+          <t>Report access problem</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>&lt;a href="https://afz.ethz.ch/recherche-archivbesuch/recherche/bibliothek.html" target="_blank" &gt;Archiv für Zeitgeschichte&lt;a&gt;</t>
+          <t>Zugriffsproblem melden</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>metagrid.link.open</t>
+          <t>eth.onlineProblem.ariaLabel</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Show Metagrid links</t>
+          <t>Report access problem by email</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Metagrid-Links zeigen</t>
+          <t>Zugriffsproblem per E-Mail melden</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>metagrid.link.close</t>
+          <t>eth.registrationLink.linkText</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Hide Metagrid links</t>
+          <t>Not registered yet?</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Metagrid-Links ausblenden</t>
+          <t>Noch nicht registriert?</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.text1</t>
+          <t>eth.onlineButton.linkText</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Article/chapter is not held in the swisscovery Network or cannot be requested.</t>
+          <t>View Online</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Artikel/Kapitel ist im swisscovery Network nicht vorhanden oder nicht bestellbar.</t>
+          <t>Online ansehen</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.text2</t>
+          <t>eth.okm.label</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Please request via</t>
+          <t>Search for “{{ search }}” in Open Knowledge Maps:</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>Bestellen Sie bitte via</t>
+          <t>Suche nach “{{ search }}” in Open Knowledge Maps:</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.text3</t>
+          <t>eth.logoSubline.subline</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>ETH swisscovery</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>ETH swisscovery</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.linkText</t>
+          <t>eth.idpWarning.text1</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>interlibrary loan</t>
+          <t>Link your SWICTH edu-ID to your ETH Zurich user account in</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>Fernleihe</t>
+          <t>Verknüpfen Sie Ihre SWITCH edu-ID mit Ihrem ETH-Benutzerkonto in</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1073,17 +1073,17 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>eth.illLink.url</t>
+          <t>eth.idpWarning.text2</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/order-forms/interlibrary-loans-ordering-copies.html</t>
+          <t>to benefit from the advantages for members of ETH Zurich.</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/bestellformulare/fernleihe-kopien-bestellen.html</t>
+          <t>, um von den Vorteilen für ETH-Angehörige zu profitieren.</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>46097.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="34">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>eth.composeErara.print</t>
+          <t>eth.idpWarning.linkText2</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Print item in ETH swisscovery</t>
+          <t>Instructions</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Print-Exemplar in ETH swisscovery</t>
+          <t>Anleitung</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>eth.composeErara.online</t>
+          <t>eth.idpWarning.linkText1</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Online item in ETH swisscovery (from e-rara)</t>
+          <t>https://www.password.ethz.ch/</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>Online-Exemplar in ETH swisscovery (e-rara)</t>
+          <t>https://www.password.ethz.ch/</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>46058.0</v>
+        <v>46260.0</v>
       </c>
     </row>
     <row r="36">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>eth.composeErara.emaps</t>
+          <t>eth.idpWarning.link1</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Georeferenced online item in ETH swisscovery (from e-maps)</t>
+          <t>https://www.password.ethz.ch/authentication/login_en.html</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>Georeferenziertes Online-Exemplar in ETH swisscovery (e-maps)</t>
+          <t>https://www.password.ethz.ch/authentication/login.html</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>46058.0</v>
+        <v>46260.0</v>
       </c>
     </row>
     <row r="37">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>eth.composeErara.geoTiff</t>
+          <t>eth.idpWarning.link2</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>GeoTIFF map via e-maps</t>
+          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/frequently-asked-questions.html#eth-card-as-user-id</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>GeoTIFF via e-maps</t>
+          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/faq.html#eth-karte-als-benutzungsausweis</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>46058.0</v>
+        <v>46163.0</v>
       </c>
     </row>
     <row r="38">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>eth.composeNb.print</t>
+          <t>eth.changeAddress.heading</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Print item in in ETH swisscovery</t>
+          <t>Address changes</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>Print-Exemplar in ETH swisscovery</t>
+          <t>Adresse bearbeiten</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>eth.composeNb.online</t>
+          <t>eth.changeAddress.ethMembers</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Online item in ETH swisscovery</t>
+          <t>Members of ETH</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>Online-Exemplar in ETH swisscovery</t>
+          <t>ETH-Angehörige</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>eth.dnbToc.toc</t>
+          <t>eth.changeAddress.ethMembersIntro</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Table of content from the DNB for</t>
+          <t>Change your address in 2 steps:</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>Inhaltsverzeichnis der DNB zu</t>
+          <t>Ändern Sie Ihre Adresse in 2 Schritten:</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>eth.dnbToc.text</t>
+          <t>eth.changeAddress.ethMembersStep1</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Content description from the DNB for</t>
+          <t>1. Change address:</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>Inhaltstext der DNB zu</t>
+          <t>1. Adresse ändern:</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>eth.libraryStack.text1</t>
+          <t>eth.changeAddress.ethMembersStep2</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Password protected access. Restricted to members of ETH Zurich only.</t>
+          <t>2. Confirm address change:</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Passwortgeschützter Zugang. Nur für Mitglieder der ETH Zürich zugänglich.</t>
+          <t>2. Adressänderung bestätigen:</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>eth.libraryStack.text2</t>
+          <t>eth.changeAddress.otherCustomers</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>You need to register with your ETH Zurich e-mail address "Sign In". Access to this source is restricted on the domain ethz.ch because of license restrictions.</t>
+          <t>Private individuals</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>Sie müssen sich mit Ihrer ETH Zürich E-Mail-Adresse unter „Anmelden” registrieren. Der Zugriff auf diese Quelle ist aufgrund von Lizenzbeschränkungen auf die Domain ethz.ch eingeschränkt.</t>
+          <t>Privatpersonen</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>eth.wayback.text</t>
+          <t>eth.changeAddress.otherCustomersIntro</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>In the web archive, select a year and a date marked in blue to access the archived website.</t>
+          <t>Change your address here:</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>Wählen Sie im Webarchiv ein Jahr und ein blau markiertes Datum, um die archivierte Website aufzurufen.</t>
+          <t>Ändern Sie Ihre Adresse hier:</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1433,17 +1433,17 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>eth.wayback.linkText</t>
+          <t>eth.changeAddress.ethMembersStep1Url</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Link to the web archive</t>
+          <t>https://idapps.ethz.ch/contact-data/</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>Link zum Webarchiv</t>
+          <t>https://idapps.ethz.ch/contact-data/</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>46058.0</v>
+        <v>46141.0</v>
       </c>
     </row>
     <row r="46">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>eth.onlineProblem.linkText</t>
+          <t>eth.changeAddress.ethMembersStep2Url</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Report access problem</t>
+          <t>https://eduid.ch</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>Zugriffsproblem melden</t>
+          <t>https://eduid.ch</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -1493,17 +1493,17 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>eth.onlineProblem.ariaLabel</t>
+          <t>eth.changeAddress.otherCustomersUrl</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Report access problem by email</t>
+          <t>https://eduid.ch</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>Zugriffsproblem per E-Mail melden</t>
+          <t>https://eduid.ch</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -1523,17 +1523,17 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>eth.registrationLink.linkText</t>
+          <t>eth.bibNews.all</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Not registered yet?</t>
+          <t>All news</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>Noch nicht registriert?</t>
+          <t>Alle News</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>eth.onlineButton.linkText</t>
+          <t>eth.geoRef.heading</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>View Online</t>
+          <t>Related Places</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>Online ansehen</t>
+          <t>Verknüpfte Orte</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>eth.okm.label</t>
+          <t>eth.geoRef.entity</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Search for “{{ search }}” in Open Knowledge Maps:</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>Suche nach “{{ search }}” in Open Knowledge Maps:</t>
+          <t>Ort</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>eth.logoSubline.subline</t>
+          <t>eth.provenance.heading</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>ETH swisscovery</t>
+          <t>Provenance marks</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>ETH swisscovery</t>
+          <t>Provenienzen</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.text1</t>
+          <t>eth.provenance.entity</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Link your SWICTH edu-ID to your ETH Zurich user account in</t>
+          <t>Provenance</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfen Sie Ihre SWITCH edu-ID mit Ihrem ETH-Benutzerkonto in</t>
+          <t>Provenienz</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.text2</t>
+          <t>eth.provenance.date</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>to benefit from the advantages for members of ETH Zurich.</t>
+          <t>Date:</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>, um von den Vorteilen für ETH-Angehörige zu profitieren.</t>
+          <t>Datierung:</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.linkText2</t>
+          <t>eth.provenance.epicsLinkText</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Instructions</t>
+          <t>Provenance in E-Pics</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>Anleitung</t>
+          <t>Provenienz in E-Pics</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -1733,17 +1733,17 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.linkText1</t>
+          <t>eth.personCard.entity</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>www.password.ethz.ch</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>www.password.ethz.ch</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.link1</t>
+          <t>eth.personCard.photo</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>https://www.password.ethz.ch/authentication/login_en.html</t>
+          <t>Photo of</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>https://www.password.ethz.ch/</t>
+          <t>Photo von</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -1793,17 +1793,17 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>eth.idpWarning.link2</t>
+          <t>eth.personCard.licence</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/en/find-media/borrowing-and-using/frequently-asked-questions.html#eth-card-as-user-id</t>
+          <t>Licence for the picture see</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>https://library.ethz.ch/medien-finden/ausleihen-und-nutzen/faq.html#eth-karte-als-benutzungsausweis</t>
+          <t>Lizenz für das Bild siehe</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>46163.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="58">
@@ -1823,17 +1823,17 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.heading</t>
+          <t>eth.personCard.heading</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Address changes</t>
+          <t>Related Persons</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>Adresse bearbeiten</t>
+          <t>Verknüpfte Personen</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembers</t>
+          <t>eth.personCard.headingMore</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Members of ETH</t>
+          <t>More related Persons</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>ETH-Angehörige</t>
+          <t>Mehr Personen</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -1883,17 +1883,17 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersIntro</t>
+          <t>eth.placePage.topics</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Change your address in 2 steps:</t>
+          <t>Topics in ETH swisscovery</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>Ändern Sie Ihre Adresse in 2 Schritten:</t>
+          <t>Geografisches Schlagwort in ETH swisscovery</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersStep1</t>
+          <t>eth.placePage.ethorama</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>1. Change address:</t>
+          <t>Documents in ETHorama</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>1. Adresse ändern:</t>
+          <t>Dokumente in ETHorama</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -1943,17 +1943,17 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersStep2</t>
+          <t>eth.placePage.ethoramaTopics</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>2. Confirm address change:</t>
+          <t>ETHorama thematic collections</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>2. Adressänderung bestätigen:</t>
+          <t>ETHorama Themensammlungen</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.otherCustomers</t>
+          <t>eth.placePage.ethoramaRoutes</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Private individuals</t>
+          <t>ETHorama historical travels</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>Privatpersonen</t>
+          <t>ETHorama Historische Reisen</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.otherCustomersIntro</t>
+          <t>eth.placePage.wikidata</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Change your address here:</t>
+          <t>Links from Wikidata</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>Ändern Sie Ihre Adresse hier:</t>
+          <t>Links from Wikidata</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2033,17 +2033,17 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersStep1Url</t>
+          <t>eth.placePage.maps</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>https://idapps.ethz.ch/contact-data/</t>
+          <t>Historical maps</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>https://idapps.ethz.ch/contact-data/</t>
+          <t>Historische Karten</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>46141.0</v>
+        <v>46058.0</v>
       </c>
     </row>
     <row r="66">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.ethMembersStep2Url</t>
+          <t>eth.placePage.mapsList</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>https://eduid.ch</t>
+          <t>Historical maps as list</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>https://eduid.ch</t>
+          <t>Historische Karten als Liste</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>eth.changeAddress.otherCustomersUrl</t>
+          <t>eth.personPage.searchVariants</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>https://eduid.ch</t>
+          <t>Search variants in all data of the ETH Library</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>https://eduid.ch</t>
+          <t>Suchvarianten in allen Daten der ETH-Bibliothek</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -2123,17 +2123,17 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>eth.bibNews.all</t>
+          <t>eth.personPage.results</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>All news</t>
+          <t>results</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>Alle News</t>
+          <t>Ergebnisse</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>eth.geoRef.heading</t>
+          <t>eth.personPage.authorityLinking</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Related Places</t>
+          <t>Authority data</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfte Orte</t>
+          <t>Normdaten</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -2183,17 +2183,17 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>eth.geoRef.entity</t>
+          <t>eth.personPage.researcherProfile</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Researcher profiles</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>Ort</t>
+          <t>Forscherprofile</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>eth.provenance.heading</t>
+          <t>eth.personPage.archives</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Provenance marks</t>
+          <t>Archives</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>Provenienzen</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>eth.provenance.entity</t>
+          <t>eth.personPage.metagrid</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Metagrid</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>Provenienz</t>
+          <t>Metagrid</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>eth.provenance.date</t>
+          <t>eth.personPage.wikidata</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Date:</t>
+          <t>Wikidata</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>Datierung:</t>
+          <t>Wikidata</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>eth.provenance.epicsLinkText</t>
+          <t>eth.personPage.prometheus</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Provenance in E-Pics</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>Provenienz in E-Pics</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.entity</t>
+          <t>eth.personPage.students</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Students (Wikidata)</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Studenten (Wikidata)</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.photo</t>
+          <t>eth.personPage.teacher</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Photo of</t>
+          <t>Teachers (Wikidata)</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>Photo von</t>
+          <t>Lehrer (Wikidata)</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.licence</t>
+          <t>eth.personPage.relatedGnd</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Licence for the picture see</t>
+          <t>Related persons from GND</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>Lizenz für das Bild siehe</t>
+          <t>Verbundene Personen nach GND</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
@@ -2423,17 +2423,17 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.heading</t>
+          <t>eth.personPage.prometheusIntro1</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Related Persons</t>
+          <t>Links from the</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>Verknüpfte Personen</t>
+          <t>Links vom</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -2453,17 +2453,17 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>eth.personCard.headingMore</t>
+          <t>slsp.offCampusWarning.41SLSP_ETH:ETH_NDE</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>More related Persons</t>
+          <t>&lt;p&gt;Licensed electronic resources of ETH Library are accessible only within the network of ETH Zurich.&lt;br&gt;&lt;a target="_blank" ng-href="https://unlimited.ethz.ch/display/WWE/Use+of+electronic+media+the+ETH+Library" rel="noopener" class="md-primoExplore-theme" href="https://unlimited.ethz.ch/display/WWE/Use+of+electronic+media+the+ETH+Library"&gt;Information about using electronic resources&lt;/a&gt; &lt;/p&gt;</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>Mehr Personen</t>
+          <t>&lt;p&gt;Lizenzierte E-Ressourcen der ETH-Bibliothek sind über das ETH-Netzwerk oder VPN zugänglich.&lt;br&gt; &lt;a target="_blank" ng-href="https://unlimited.ethz.ch/display/WWE/Use+of+electronic+media+the+ETH+Library" rel="noopener" class="md-primoExplore-theme" href="https://unlimited.ethz.ch/display/WWE/Use+of+electronic+media+the+ETH+Library"&gt;Informationen zur Nutzung elektronischer Ressourcen&lt;/a&gt; &lt;/p&gt;</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>46058.0</v>
+        <v>46253.0</v>
       </c>
     </row>
     <row r="80">
@@ -2483,17 +2483,17 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.topics</t>
+          <t>eth.personPage.prometheusIntro2</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Topics in ETH swisscovery</t>
+          <t>Aggregator of the</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>Geografisches Schlagwort in ETH swisscovery</t>
+          <t>Aggregator des</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -2513,17 +2513,17 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.ethorama</t>
+          <t>eth.personPage.prometheusIntro3</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Documents in ETHorama</t>
+          <t>LMU Center for Digital Humanities</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>Dokumente in ETHorama</t>
+          <t>LMU Center for Digital Humanities</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.ethoramaTopics</t>
+          <t>eth.personPage.searchName</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>ETHorama thematic collections</t>
+          <t>Search by name</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>ETHorama Themensammlungen</t>
+          <t>Suche nach Namen</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -2573,17 +2573,17 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.ethoramaRoutes</t>
+          <t>eth.personPage.searchGnd</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>ETHorama historical travels</t>
+          <t>Search by GND ID</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>ETHorama Historische Reisen</t>
+          <t>Suche nach GND ID</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -2603,17 +2603,17 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.wikidata</t>
+          <t>eth.personPage.searchGndBirth</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Links from Wikidata</t>
+          <t>Search by name and (GND ID or birthyear)</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>Links from Wikidata</t>
+          <t>Suche nach Name und (GND ID oder Geburtsjahr)</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.maps</t>
+          <t>eth.personPage.born</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Historical maps</t>
+          <t>Born:</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>Historische Karten</t>
+          <t>Geboren:</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>eth.placePage.mapsList</t>
+          <t>eth.personPage.prometheusAll</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Historical maps as list</t>
+          <t>All links from Prometheus</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>Historische Karten als Liste</t>
+          <t>Alle Links von Prometheus</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.searchVariants</t>
+          <t>eth.provenienzEraraLink.erara</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>Search variants in all data of the ETH Library</t>
+          <t>Source in e-rara</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>Suchvarianten in allen Daten der ETH-Bibliothek</t>
+          <t>Quelle in e-rara</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.results</t>
+          <t>eth.provenienzEraraLink.swisscovery</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>results</t>
+          <t>Details provenance mark</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>Ergebnisse</t>
+          <t>Details Provenienzvermerk</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -2753,17 +2753,17 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.authorityLinking</t>
+          <t>eth.bibNews.heading</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>Authority data</t>
+          <t>News</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>Normdaten</t>
+          <t>News</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -2783,17 +2783,17 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.researcherProfile</t>
+          <t>eth.gitHint.heading</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>Researcher profiles</t>
+          <t>important information</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>Forscherprofile</t>
+          <t>Wichtiger Hinweis</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -2813,17 +2813,17 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.archives</t>
+          <t>eth.locationLink.website</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>Archives</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Webseite</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.metagrid</t>
+          <t>eth.rapidoEthmemberHint.text</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Metagrid</t>
+          <t>Please check in the upper ordering section if one of the libraries at ETH Zurich offers "Digitization" (free service).</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>Metagrid</t>
+          <t>Überprüfen Sie bitte im oberen Bestellbereich, ob eine Bibliothek der ETH Zürich "Digitalisierung" anbietet (kostenloser Service).</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>46058.0</v>
+        <v>46108.0</v>
       </c>
     </row>
     <row r="93">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.wikidata</t>
+          <t>41SLSP_ETH:TMI_NDE.eth.composeNb.print</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Wikidata</t>
+          <t>Print item in TMI Research</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>Wikidata</t>
+          <t>Print-Exemplar in TMI Research</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>46058.0</v>
+        <v>46113.0</v>
       </c>
     </row>
     <row r="94">
@@ -2903,17 +2903,17 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheus</t>
+          <t>slsp.topbarMessage.message.41SLSP_ETH:ETH_NDE</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>NOT_DEFINED</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>NOT_DEFINED</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>46058.0</v>
+        <v>46240.0</v>
       </c>
     </row>
     <row r="95">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.students</t>
+          <t>41SLSP_ETH:TMI_NDE.eth.composeNb.online</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>Students (Wikidata)</t>
+          <t>Online item in TMI Research</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>Studenten (Wikidata)</t>
+          <t>Online-Exemplar in TMI Research</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>46058.0</v>
+        <v>46113.0</v>
       </c>
     </row>
     <row r="96">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.teacher</t>
+          <t>41SLSP_ETH:TMI_NDE.eth.logoSubline.subline</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>Teachers (Wikidata)</t>
+          <t>TMI Research</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>Lehrer (Wikidata)</t>
+          <t>TMI Research</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>46058.0</v>
+        <v>46113.0</v>
       </c>
     </row>
     <row r="97">
@@ -2993,17 +2993,17 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.relatedGnd</t>
+          <t>eth.requestHint.request</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>Related persons from GND</t>
+          <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00 (free of charge to ETH institutional address)</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>Verbundene Personen nach GND</t>
+          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00 (kostenlos an ETH-Institutsadresse)</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>46058.0</v>
+        <v>46141.0</v>
       </c>
     </row>
     <row r="98">
@@ -3023,17 +3023,17 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheusIntro1</t>
+          <t>eth.requestHint.digitization</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Links from the</t>
+          <t>Normal fee: CHF 5.00&lt;br&gt;ETH employees: free of charge&lt;br&gt;All students: CHF 2.50&lt;br&gt;Commercial clients: CHF 25.00</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Links vom</t>
+          <t>Normale Gebühr: CHF 5.00&lt;br&gt;ETH-Mitarbeitende: kostenlos&lt;br&gt;Alle Studierende: CHF 2.50&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>46058.0</v>
+        <v>46141.0</v>
       </c>
     </row>
     <row r="99">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheusIntro2</t>
+          <t>tmi.getit.E73BI</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>Aggregator of the</t>
+          <t>&lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;Can be used in the reading room of the Thomas Mann Archives subject to prior appointment.&lt;/div&gt; &lt;div&gt;Contact: &lt;a href="mailto:tma@library.ethz.ch?subject=Appointment for: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH_NDE&amp;docid=alma{{id}}"&gt;         &lt;span&gt;More Informations in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>Aggregator des</t>
+          <t>&lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;Benutzung im Lesesaal des Thomas-Mann-Archivs auf Voranmeldung.&lt;/div&gt; &lt;div&gt;Kontakt: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH_NDE&amp;docid=alma{{id}}"&gt;         &lt;span&gt;Mehr Informationen in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>46058.0</v>
+        <v>46184.0</v>
       </c>
     </row>
     <row r="100">
@@ -3083,17 +3083,17 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheusIntro3</t>
+          <t>eth.requestHint.digitizationOtherLibrary</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>LMU Center for Digital Humanities</t>
+          <t>Normal fee: CHF 5.00&lt;br&gt;Commercial clients: CHF 25.00</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>LMU Center for Digital Humanities</t>
+          <t>Normale Gebühr: CHF 5.00&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>46058.0</v>
+        <v>46142.0</v>
       </c>
     </row>
     <row r="101">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.searchName</t>
+          <t>tmi.getit.tmhla</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>Search by name</t>
+          <t>&lt;div&gt;       &lt;span&gt;Not loanable.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Can be used in the library of the Thomas Mann House by prior appointment. Please contact&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Request about: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>Suche nach Namen</t>
+          <t>&lt;div&gt;  &lt;span&gt;Nicht ausleihbar.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Benutzung nach vorheriger Anmeldung in der Bibliothek des Thomas-Mann-Hauses. Bitte kontaktieren Sie&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Anfrage zu: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>46058.0</v>
+        <v>46149.0</v>
       </c>
     </row>
     <row r="102">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.searchGnd</t>
+          <t>eth.requestHint.requestOtherLibrary</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Search by GND ID</t>
+          <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>Suche nach GND ID</t>
+          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>46058.0</v>
+        <v>46142.0</v>
       </c>
     </row>
     <row r="103">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.searchGndBirth</t>
+          <t>tmi.getit.luebeck</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Search by name and (GND ID or birthyear)</t>
+          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailed information in the online database of the Buddenbrookhaus     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Not possible to order.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digital copies can be requested from Buddenbrookhaus (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Request about: {{callNumber}}"&gt;Contact&lt;/a&gt; ).     &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>Suche nach Name und (GND ID oder Geburtsjahr)</t>
+          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailinformationen in der Online-Datenbank des Buddenbrookhauses     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Keine Bestellung möglich.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digitalisate können beim Buddenbrookhaus angefragt werden (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Anfrage zu: {{callNumber}}"&gt;Kontakt&lt;/a&gt; ).     &lt;/div&gt;</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>46058.0</v>
+        <v>46149.0</v>
       </c>
     </row>
     <row r="104">
@@ -3203,17 +3203,17 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.born</t>
+          <t>tmi.viewit.monacensia</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>Born:</t>
+          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;Detailed information in the Kalliope Union Catalog (metadata only) &lt;/a&gt; &lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;     Archival materials can be viewed on site at the Monacensia im Hildebrandhaus (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Request digitized copy with signature: {{callNumber}}"&gt;       Contact     &lt;/a&gt; ). &lt;/div&gt;</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>Geboren:</t>
+          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;     Detailinformationen in der Online-Datenbank der Monacensia im Hildebrandhaus (nur Metadaten) &lt;/a&gt; &lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;     Archivalien können vor Ort in der Monacensia im Hildebrandhaus eingesehen werden (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Anfrage Digitalisat mit Signatur "{{callNumber}}""&gt;       Kontakt     &lt;/a&gt; ). &lt;/div&gt;</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>46058.0</v>
+        <v>46155.0</v>
       </c>
     </row>
     <row r="105">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>eth.personPage.prometheusAll</t>
+          <t>tmi.viewit.monacensia.heading</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>All links from Prometheus</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>Alle Links von Prometheus</t>
+          <t>Zugang</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>46058.0</v>
+        <v>46155.0</v>
       </c>
     </row>
     <row r="106">
@@ -3263,17 +3263,17 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>eth.provenienzEraraLink.erara</t>
+          <t>41SLSP_ETH:TMI_NDE.nde.landing.header</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>Source in e-rara</t>
+          <t>NOT_DEFINED</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>Quelle in e-rara</t>
+          <t>NOT_DEFINED</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>46058.0</v>
+        <v>46164.0</v>
       </c>
     </row>
     <row r="107">
@@ -3293,17 +3293,17 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>eth.provenienzEraraLink.swisscovery</t>
+          <t>eth.onlineProblem.mail</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>Details provenance mark</t>
+          <t>almakb@library.ethz.ch</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>Details Provenienzvermerk</t>
+          <t>almakb@library.ethz.ch</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>46058.0</v>
+        <v>46169.0</v>
       </c>
     </row>
     <row r="108">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>eth.bibNews.heading</t>
+          <t>tmi.topbarMessage.message</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>TMI EN:✨das und das momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>TMI DE:✨das und das  nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>46058.0</v>
+        <v>46178.0</v>
       </c>
     </row>
     <row r="109">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>eth.gitHint.heading</t>
+          <t>tmi.topbarMessage.heading</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>important information</t>
+          <t>Important information</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46058.0</v>
+        <v>46178.0</v>
       </c>
     </row>
     <row r="110">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>eth.locationLink.website</t>
+          <t>tmi.composeErara.print</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Print item in in ETH swisscovery</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>Webseite</t>
+          <t>Print-Exemplar in TMI Research</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46058.0</v>
+        <v>46190.0</v>
       </c>
     </row>
     <row r="111">
@@ -3413,17 +3413,17 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>eth.rapidoEthmemberHint.text</t>
+          <t>tmi.composeErara.online</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>Please check in the upper ordering section if one of the libraries at ETH Zurich offers "Digitization" (free service).</t>
+          <t>Online item in in ETH swisscovery</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>Überprüfen Sie bitte im oberen Bestellbereich, ob eine Bibliothek der ETH Zürich "Digitalisierung" anbietet (kostenloser Service).</t>
+          <t>Online-Exemplar in TMI Research</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
@@ -3432,641 +3432,11 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>46108.0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>41SLSP_ETH:TMI_NDE.eth.composeNb.print</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>Print item in TMI Research</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>Print-Exemplar in TMI Research</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>46113.0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>41SLSP_ETH:TMI_NDE.eth.composeNb.online</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>Online item in TMI Research</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>Online-Exemplar in TMI Research</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>46113.0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>41SLSP_ETH:TMI_NDE.eth.logoSubline.subline</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>TMI Research</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>TMI Research</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>46113.0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>eth.requestHint.request</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00 (free of charge to ETH institutional address)</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00 (kostenlos an ETH-Institutsadresse)</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>46141.0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>eth.requestHint.digitization</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>Normal fee: CHF 5.00&lt;br&gt;ETH employees: free of charge&lt;br&gt;All students: CHF 2.50&lt;br&gt;Commercial clients: CHF 25.00</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>Normale Gebühr: CHF 5.00&lt;br&gt;ETH-Mitarbeitende: kostenlos&lt;br&gt;Alle Studierende: CHF 2.50&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>46141.0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>tmi.getit.E73BI</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;Can be used in the reading room of the Thomas Mann Archives subject to prior appointment.&lt;/div&gt; &lt;div&gt;Contact: &lt;a href="mailto:tma@library.ethz.ch?subject=Appointment for: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH_NDE&amp;docid=alma{{id}}"&gt;         &lt;span&gt;More Informations in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;Benutzung im Lesesaal des Thomas-Mann-Archivs auf Voranmeldung.&lt;/div&gt; &lt;div&gt;Kontakt: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für: {{callNumber}}"&gt;tma@library.ethz.ch&lt;/a&gt;&lt;/div&gt; &lt;div&gt;     &lt;a target="_blank" href="https://slsp-eth.primo.exlibrisgroup.com/nde/fulldisplay?vid=41SLSP_ETH:ETH_NDE&amp;docid=alma{{id}}"&gt;         &lt;span&gt;Mehr Informationen in ETH swisscovery&lt;/span&gt;     &lt;/a&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>46184.0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>eth.requestHint.digitizationOtherLibrary</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>Normal fee: CHF 5.00&lt;br&gt;Commercial clients: CHF 25.00</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>Normale Gebühr: CHF 5.00&lt;br&gt;Kommerzielle Unternehmen: CHF 25.00</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>46142.0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>tmi.getit.tmhla</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;       &lt;span&gt;Not loanable.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Can be used in the library of the Thomas Mann House by prior appointment. Please contact&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Request about: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;  &lt;span&gt;Nicht ausleihbar.&lt;/span&gt;   &lt;/div&gt;   &lt;div&gt;       &lt;span&gt;Benutzung nach vorheriger Anmeldung in der Bibliothek des Thomas-Mann-Hauses. Bitte kontaktieren Sie&lt;/span&gt;       &lt;a href="mailto:thomasmannhouse@vatmh.org?subject=Anfrage zu: {{callNumber}}"&gt;           &lt;span&gt;thomasmannhouse@vatmh.org&lt;/span&gt;       &lt;/a&gt;          &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>46149.0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>eth.requestHint.requestOtherLibrary</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>Pickup on site: free of charge&lt;br&gt;Postal delivery: CHF 12.00</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>Abholung vor Ort: kostenlos&lt;br&gt;Postversand: CHF 12.00</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>46142.0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>tmi.getit.luebeck</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailed information in the online database of the Buddenbrookhaus     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Not possible to order.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digital copies can be requested from Buddenbrookhaus (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Request about: {{callNumber}}"&gt;Contact&lt;/a&gt; ).     &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>&lt;a target="_blank" href="https://archiv-buddenbrookhaus.luebeck.de/objekt_start.fau?prj=buddenbrookhaus&amp;dm={{dm}}&amp;ref={{id}}"&gt;         Detailinformationen in der Online-Datenbank des Buddenbrookhauses     &lt;/a&gt;     &lt;div&gt;         &lt;span&gt;Keine Bestellung möglich.&lt;/span&gt;     &lt;/div&gt;     &lt;div&gt;Digitalisate können beim Buddenbrookhaus angefragt werden (                 &lt;a href="mailto:britta.dittmann@luebeck.de?subject=Anfrage zu: {{callNumber}}"&gt;Kontakt&lt;/a&gt; ).     &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>46149.0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>tmi.viewit.monacensia</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;Detailed information in the Kalliope Union Catalog (metadata only) &lt;/a&gt; &lt;div&gt;No request possible.&lt;/div&gt; &lt;div&gt;     Archival materials can be viewed on site at the Monacensia im Hildebrandhaus (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Request digitized copy with signature: {{callNumber}}"&gt;       Contact     &lt;/a&gt; ). &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>&lt;a target="_blank" rel="noopener" href="{{link}}"&gt;     Detailinformationen in der Online-Datenbank der Monacensia im Hildebrandhaus (nur Metadaten) &lt;/a&gt; &lt;div&gt;Keine Bestellung möglich.&lt;/div&gt; &lt;div&gt;     Archivalien können vor Ort in der Monacensia im Hildebrandhaus eingesehen werden (     &lt;a href="mailto:monacensia.literaturarchiv@muenchen.de?subject=Anfrage Digitalisat mit Signatur "{{callNumber}}""&gt;       Kontakt     &lt;/a&gt; ). &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>46155.0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>tmi.viewit.monacensia.heading</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>Access</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>Zugang</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>46155.0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>41SLSP_ETH:TMI_NDE.nde.landing.header</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>NOT_DEFINED</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>NOT_DEFINED</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>46164.0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>eth.onlineProblem.mail</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>almakb@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>almakb@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>46169.0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>eth.topbarMessage.message</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>EN:✨Bücherbestellungen unter 'Weitere Bestelloptionen' momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>DE:✨Bücherbestellungen unter 'Weitere Bestelloptionen' momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>46183.0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t>eth.topbarMessage.heading</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr">
-        <is>
-          <t>Important information</t>
-        </is>
-      </c>
-      <c r="D127" s="1" t="inlineStr">
-        <is>
-          <t>Wichtiger Hinweis</t>
-        </is>
-      </c>
-      <c r="E127" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>46176.0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>eth.topbarMessage.message.41SLSP_ETH:ETH_CUSTOMIZING</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>ETH View:✨Bücherbestellungen unter 'Weitere Bestelloptionen' momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>Testen Sie die Beta-Version des neuen KI-gestützten Research Assistant!  &lt;a href=\"https://library.ethz.ch/en/searching-and-using/research-assistant.html\" target=\"_blank\"&gt;Learn more&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>46177.0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>tmi.topbarMessage.message</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>TMI EN:✨das und das momentan nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>TMI DE:✨das und das  nicht möglich.  &lt;a href="https://library.ethz.ch/recherchieren-und-nutzen/research-assistant.html" target="_blank"&gt;Mehr erfahren&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>46178.0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>tmi.topbarMessage.heading</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>Important information</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>Wichtiger Hinweis</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>46178.0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>tmi.composeErara.print</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>Print item in in ETH swisscovery</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>Print-Exemplar in TMI Research</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="n">
         <v>46190.0</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>tmi.composeErara.online</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>Online item in in ETH swisscovery</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>Online-Exemplar in TMI Research</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>46190.0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F132"/>
+  <autoFilter ref="A1:F111"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>
